--- a/xlsx/tests/templates/gantt_project_tracker.xlsx
+++ b/xlsx/tests/templates/gantt_project_tracker.xlsx
@@ -1,25 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dg-ac/Documents/IronCalc/xlsx/tests/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D89AB0B5-0349-D14B-94B7-F49E933AD94B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED65086A-AC33-4FE2-96F5-F1EB64166A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan" sheetId="2" r:id="rId1"/>
     <sheet name="Tasks" sheetId="3" r:id="rId2"/>
     <sheet name="Settings" sheetId="1" r:id="rId3"/>
+    <sheet name="METADATA" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -58,7 +61,142 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="61">
+  <si>
+    <t>Jun 2025</t>
+  </si>
+  <si>
+    <t>Jul 2025</t>
+  </si>
+  <si>
+    <t>Aug 2025</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>Task</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>Days</t>
+  </si>
+  <si>
+    <t>End</t>
+  </si>
+  <si>
+    <t>% Done</t>
+  </si>
+  <si>
+    <t>TASK INPUT</t>
+  </si>
+  <si>
+    <t>Edit here (plan updates automatically) / Blue cells = your inputs  /  End Date is calculated / Overdue tasks are marked in red</t>
+  </si>
+  <si>
+    <t>Task Name</t>
+  </si>
+  <si>
+    <t>Start Date</t>
+  </si>
+  <si>
+    <t>End Date</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Planning</t>
+  </si>
+  <si>
+    <t>Define scope &amp; goals</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Stakeholder interviews</t>
+  </si>
+  <si>
+    <t>Requirements doc</t>
+  </si>
+  <si>
+    <t>Tech stack decision</t>
+  </si>
+  <si>
+    <t>Jane</t>
+  </si>
+  <si>
+    <t>Design</t>
+  </si>
+  <si>
+    <t>UX wireframes</t>
+  </si>
+  <si>
+    <t>Design system / tokens</t>
+  </si>
+  <si>
+    <t>Prototype review</t>
+  </si>
+  <si>
+    <t>Dev</t>
+  </si>
+  <si>
+    <t>Spreadsheet engine core</t>
+  </si>
+  <si>
+    <t>Formula parser v2</t>
+  </si>
+  <si>
+    <t>Frontend components</t>
+  </si>
+  <si>
+    <t>WebAssembly build</t>
+  </si>
+  <si>
+    <t>API integration</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>Unit test suite</t>
+  </si>
+  <si>
+    <t>Cross-browser QA</t>
+  </si>
+  <si>
+    <t>Performance benchmarks</t>
+  </si>
+  <si>
+    <t>Bug fixes</t>
+  </si>
+  <si>
+    <t>Launch</t>
+  </si>
+  <si>
+    <t>Docs &amp; changelog</t>
+  </si>
+  <si>
+    <t>Beta release</t>
+  </si>
+  <si>
+    <t>Marketing page</t>
+  </si>
+  <si>
+    <t>v1.0 release 🚀</t>
+  </si>
+  <si>
+    <t>PROJECT SETTINGS</t>
+  </si>
   <si>
     <t>Project Name</t>
   </si>
@@ -84,6 +222,9 @@
     <t>Today</t>
   </si>
   <si>
+    <t>Auto, do not edit</t>
+  </si>
+  <si>
     <t>Owner 1</t>
   </si>
   <si>
@@ -99,145 +240,10 @@
     <t>Phase colours (reference)</t>
   </si>
   <si>
-    <t>Planning</t>
-  </si>
-  <si>
-    <t>Design</t>
-  </si>
-  <si>
-    <t>Testing</t>
-  </si>
-  <si>
-    <t>Launch</t>
-  </si>
-  <si>
     <t>Other</t>
   </si>
   <si>
-    <t>Start</t>
-  </si>
-  <si>
-    <t>% Done</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>Phase</t>
-  </si>
-  <si>
-    <t>Task</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>Days</t>
-  </si>
-  <si>
-    <t>End</t>
-  </si>
-  <si>
-    <t>Jun 2025</t>
-  </si>
-  <si>
-    <t>Jul 2025</t>
-  </si>
-  <si>
-    <t>Aug 2025</t>
-  </si>
-  <si>
-    <t>Task Name</t>
-  </si>
-  <si>
-    <t>Start Date</t>
-  </si>
-  <si>
-    <t>End Date</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Define scope &amp; goals</t>
-  </si>
-  <si>
-    <t>Stakeholder interviews</t>
-  </si>
-  <si>
-    <t>Requirements doc</t>
-  </si>
-  <si>
-    <t>Tech stack decision</t>
-  </si>
-  <si>
-    <t>UX wireframes</t>
-  </si>
-  <si>
-    <t>Design system / tokens</t>
-  </si>
-  <si>
-    <t>Prototype review</t>
-  </si>
-  <si>
-    <t>Spreadsheet engine core</t>
-  </si>
-  <si>
-    <t>Formula parser v2</t>
-  </si>
-  <si>
-    <t>Frontend components</t>
-  </si>
-  <si>
-    <t>WebAssembly build</t>
-  </si>
-  <si>
-    <t>API integration</t>
-  </si>
-  <si>
-    <t>Unit test suite</t>
-  </si>
-  <si>
-    <t>Cross-browser QA</t>
-  </si>
-  <si>
-    <t>Performance benchmarks</t>
-  </si>
-  <si>
-    <t>Bug fixes</t>
-  </si>
-  <si>
-    <t>Docs &amp; changelog</t>
-  </si>
-  <si>
-    <t>Beta release</t>
-  </si>
-  <si>
-    <t>Marketing page</t>
-  </si>
-  <si>
-    <t>v1.0 release 🚀</t>
-  </si>
-  <si>
-    <t>Dev</t>
-  </si>
-  <si>
-    <t>PROJECT SETTINGS</t>
-  </si>
-  <si>
-    <t>TASK INPUT</t>
-  </si>
-  <si>
-    <t>Edit here (plan updates automatically) / Blue cells = your inputs  /  End Date is calculated / Overdue tasks are marked in red</t>
-  </si>
-  <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>Jane</t>
-  </si>
-  <si>
-    <t>Auto, do not edit</t>
+    <t>NOW</t>
   </si>
 </sst>
 </file>
@@ -245,10 +251,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="d"/>
-    <numFmt numFmtId="168" formatCode="m/d/yy"/>
+    <numFmt numFmtId="164" formatCode="d"/>
+    <numFmt numFmtId="165" formatCode="m/d/yy"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -620,7 +626,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -634,7 +640,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -643,7 +649,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -655,22 +661,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -679,16 +676,10 @@
     <xf numFmtId="9" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="21" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -705,9 +696,6 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="21" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -727,6 +715,25 @@
     <xf numFmtId="0" fontId="28" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="21" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -749,13 +756,12 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="21" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="21" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -774,7 +780,8 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1303,421 +1310,427 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CC40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" customWidth="1"/>
-    <col min="2" max="2" width="8.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.1640625" style="1" customWidth="1"/>
-    <col min="4" max="8" width="8.83203125" customWidth="1"/>
-    <col min="9" max="78" width="2.1640625" customWidth="1"/>
+    <col min="1" max="1" width="2.85546875" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" style="1" customWidth="1"/>
+    <col min="4" max="8" width="8.85546875" customWidth="1"/>
+    <col min="9" max="78" width="2.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:81" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="39" t="str">
+    <row r="1" spans="1:81" ht="25.5" customHeight="1">
+      <c r="A1" s="40" t="str">
         <f>Settings!B2&amp;"  ·  PROJECT PLAN"</f>
         <v>IronCalc v1.0  ·  PROJECT PLAN</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="40"/>
-      <c r="P1" s="40"/>
-      <c r="Q1" s="40"/>
-      <c r="R1" s="40"/>
-      <c r="S1" s="40"/>
-      <c r="T1" s="40"/>
-      <c r="U1" s="40"/>
-      <c r="V1" s="40"/>
-      <c r="W1" s="40"/>
-      <c r="X1" s="40"/>
-      <c r="Y1" s="40"/>
-      <c r="Z1" s="40"/>
-      <c r="AA1" s="40"/>
-      <c r="AB1" s="40"/>
-      <c r="AC1" s="40"/>
-      <c r="AD1" s="40"/>
-      <c r="AE1" s="40"/>
-      <c r="AF1" s="40"/>
-      <c r="AG1" s="40"/>
-      <c r="AH1" s="40"/>
-      <c r="AI1" s="40"/>
-      <c r="AJ1" s="40"/>
-      <c r="AK1" s="40"/>
-      <c r="AL1" s="40"/>
-      <c r="AM1" s="40"/>
-      <c r="AN1" s="40"/>
-      <c r="AO1" s="40"/>
-      <c r="AP1" s="40"/>
-      <c r="AQ1" s="40"/>
-      <c r="AR1" s="40"/>
-      <c r="AS1" s="40"/>
-      <c r="AT1" s="40"/>
-      <c r="AU1" s="40"/>
-      <c r="AV1" s="40"/>
-      <c r="AW1" s="40"/>
-      <c r="AX1" s="40"/>
-      <c r="AY1" s="40"/>
-      <c r="AZ1" s="40"/>
-      <c r="BA1" s="40"/>
-      <c r="BB1" s="40"/>
-      <c r="BC1" s="40"/>
-      <c r="BD1" s="40"/>
-      <c r="BE1" s="40"/>
-      <c r="BF1" s="40"/>
-      <c r="BG1" s="40"/>
-      <c r="BH1" s="40"/>
-      <c r="BI1" s="40"/>
-      <c r="BJ1" s="40"/>
-      <c r="BK1" s="40"/>
-      <c r="BL1" s="40"/>
-      <c r="BM1" s="40"/>
-      <c r="BN1" s="40"/>
-      <c r="BO1" s="40"/>
-      <c r="BP1" s="40"/>
-      <c r="BQ1" s="40"/>
-      <c r="BR1" s="40"/>
-      <c r="BS1" s="40"/>
-      <c r="BT1" s="40"/>
-      <c r="BU1" s="40"/>
-      <c r="BV1" s="40"/>
-      <c r="BW1" s="40"/>
-      <c r="BX1" s="40"/>
-      <c r="BY1" s="40"/>
-      <c r="BZ1" s="40"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="41"/>
+      <c r="U1" s="41"/>
+      <c r="V1" s="41"/>
+      <c r="W1" s="41"/>
+      <c r="X1" s="41"/>
+      <c r="Y1" s="41"/>
+      <c r="Z1" s="41"/>
+      <c r="AA1" s="41"/>
+      <c r="AB1" s="41"/>
+      <c r="AC1" s="41"/>
+      <c r="AD1" s="41"/>
+      <c r="AE1" s="41"/>
+      <c r="AF1" s="41"/>
+      <c r="AG1" s="41"/>
+      <c r="AH1" s="41"/>
+      <c r="AI1" s="41"/>
+      <c r="AJ1" s="41"/>
+      <c r="AK1" s="41"/>
+      <c r="AL1" s="41"/>
+      <c r="AM1" s="41"/>
+      <c r="AN1" s="41"/>
+      <c r="AO1" s="41"/>
+      <c r="AP1" s="41"/>
+      <c r="AQ1" s="41"/>
+      <c r="AR1" s="41"/>
+      <c r="AS1" s="41"/>
+      <c r="AT1" s="41"/>
+      <c r="AU1" s="41"/>
+      <c r="AV1" s="41"/>
+      <c r="AW1" s="41"/>
+      <c r="AX1" s="41"/>
+      <c r="AY1" s="41"/>
+      <c r="AZ1" s="41"/>
+      <c r="BA1" s="41"/>
+      <c r="BB1" s="41"/>
+      <c r="BC1" s="41"/>
+      <c r="BD1" s="41"/>
+      <c r="BE1" s="41"/>
+      <c r="BF1" s="41"/>
+      <c r="BG1" s="41"/>
+      <c r="BH1" s="41"/>
+      <c r="BI1" s="41"/>
+      <c r="BJ1" s="41"/>
+      <c r="BK1" s="41"/>
+      <c r="BL1" s="41"/>
+      <c r="BM1" s="41"/>
+      <c r="BN1" s="41"/>
+      <c r="BO1" s="41"/>
+      <c r="BP1" s="41"/>
+      <c r="BQ1" s="41"/>
+      <c r="BR1" s="41"/>
+      <c r="BS1" s="41"/>
+      <c r="BT1" s="41"/>
+      <c r="BU1" s="41"/>
+      <c r="BV1" s="41"/>
+      <c r="BW1" s="41"/>
+      <c r="BX1" s="41"/>
+      <c r="BY1" s="41"/>
+      <c r="BZ1" s="41"/>
+      <c r="CA1" s="38"/>
+      <c r="CB1" s="38"/>
+      <c r="CC1" s="38"/>
     </row>
-    <row r="2" spans="1:81" s="2" customFormat="1" ht="10.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="41"/>
-      <c r="S2" s="41"/>
-      <c r="T2" s="41"/>
-      <c r="U2" s="41"/>
-      <c r="V2" s="41"/>
-      <c r="W2" s="41"/>
-      <c r="X2" s="41"/>
-      <c r="Y2" s="41"/>
-      <c r="Z2" s="41"/>
-      <c r="AA2" s="41"/>
-      <c r="AB2" s="41"/>
-      <c r="AC2" s="41"/>
-      <c r="AD2" s="41"/>
-      <c r="AE2" s="41"/>
-      <c r="AF2" s="41"/>
-      <c r="AG2" s="41"/>
-      <c r="AH2" s="41"/>
-      <c r="AI2" s="41"/>
-      <c r="AJ2" s="41"/>
-      <c r="AK2" s="41"/>
-      <c r="AL2" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="AM2" s="41"/>
-      <c r="AN2" s="41"/>
-      <c r="AO2" s="41"/>
-      <c r="AP2" s="41"/>
-      <c r="AQ2" s="41"/>
-      <c r="AR2" s="41"/>
-      <c r="AS2" s="41"/>
-      <c r="AT2" s="41"/>
-      <c r="AU2" s="41"/>
-      <c r="AV2" s="41"/>
-      <c r="AW2" s="41"/>
-      <c r="AX2" s="41"/>
-      <c r="AY2" s="41"/>
-      <c r="AZ2" s="41"/>
-      <c r="BA2" s="41"/>
-      <c r="BB2" s="41"/>
-      <c r="BC2" s="41"/>
-      <c r="BD2" s="41"/>
-      <c r="BE2" s="41"/>
-      <c r="BF2" s="41"/>
-      <c r="BG2" s="41"/>
-      <c r="BH2" s="41"/>
-      <c r="BI2" s="41"/>
-      <c r="BJ2" s="41"/>
-      <c r="BK2" s="41"/>
-      <c r="BL2" s="41"/>
-      <c r="BM2" s="41"/>
-      <c r="BN2" s="41"/>
-      <c r="BO2" s="41"/>
-      <c r="BP2" s="41"/>
-      <c r="BQ2" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="BR2" s="41"/>
-      <c r="BS2" s="41"/>
-      <c r="BT2" s="41"/>
-      <c r="BU2" s="41"/>
-      <c r="BV2" s="41"/>
-      <c r="BW2" s="41"/>
-      <c r="BX2" s="41"/>
-      <c r="BY2" s="41"/>
-      <c r="BZ2" s="41"/>
+    <row r="2" spans="1:81" s="2" customFormat="1" ht="10.35" customHeight="1">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="42"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="42"/>
+      <c r="P2" s="42"/>
+      <c r="Q2" s="42"/>
+      <c r="R2" s="42"/>
+      <c r="S2" s="42"/>
+      <c r="T2" s="42"/>
+      <c r="U2" s="42"/>
+      <c r="V2" s="42"/>
+      <c r="W2" s="42"/>
+      <c r="X2" s="42"/>
+      <c r="Y2" s="42"/>
+      <c r="Z2" s="42"/>
+      <c r="AA2" s="42"/>
+      <c r="AB2" s="42"/>
+      <c r="AC2" s="42"/>
+      <c r="AD2" s="42"/>
+      <c r="AE2" s="42"/>
+      <c r="AF2" s="42"/>
+      <c r="AG2" s="42"/>
+      <c r="AH2" s="42"/>
+      <c r="AI2" s="42"/>
+      <c r="AJ2" s="42"/>
+      <c r="AK2" s="42"/>
+      <c r="AL2" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM2" s="42"/>
+      <c r="AN2" s="42"/>
+      <c r="AO2" s="42"/>
+      <c r="AP2" s="42"/>
+      <c r="AQ2" s="42"/>
+      <c r="AR2" s="42"/>
+      <c r="AS2" s="42"/>
+      <c r="AT2" s="42"/>
+      <c r="AU2" s="42"/>
+      <c r="AV2" s="42"/>
+      <c r="AW2" s="42"/>
+      <c r="AX2" s="42"/>
+      <c r="AY2" s="42"/>
+      <c r="AZ2" s="42"/>
+      <c r="BA2" s="42"/>
+      <c r="BB2" s="42"/>
+      <c r="BC2" s="42"/>
+      <c r="BD2" s="42"/>
+      <c r="BE2" s="42"/>
+      <c r="BF2" s="42"/>
+      <c r="BG2" s="42"/>
+      <c r="BH2" s="42"/>
+      <c r="BI2" s="42"/>
+      <c r="BJ2" s="42"/>
+      <c r="BK2" s="42"/>
+      <c r="BL2" s="42"/>
+      <c r="BM2" s="42"/>
+      <c r="BN2" s="42"/>
+      <c r="BO2" s="42"/>
+      <c r="BP2" s="42"/>
+      <c r="BQ2" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="BR2" s="42"/>
+      <c r="BS2" s="42"/>
+      <c r="BT2" s="42"/>
+      <c r="BU2" s="42"/>
+      <c r="BV2" s="42"/>
+      <c r="BW2" s="42"/>
+      <c r="BX2" s="42"/>
+      <c r="BY2" s="42"/>
+      <c r="BZ2" s="42"/>
     </row>
-    <row r="3" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="19">
+    <row r="3" spans="1:81" ht="15.95" customHeight="1">
+      <c r="A3" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="16">
         <v>45810</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="16">
         <v>45811</v>
       </c>
-      <c r="K3" s="19">
+      <c r="K3" s="16">
         <v>45812</v>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="16">
         <v>45813</v>
       </c>
-      <c r="M3" s="19">
+      <c r="M3" s="16">
         <v>45814</v>
       </c>
-      <c r="N3" s="19">
+      <c r="N3" s="16">
         <v>45815</v>
       </c>
-      <c r="O3" s="19">
+      <c r="O3" s="16">
         <v>45816</v>
       </c>
-      <c r="P3" s="19">
+      <c r="P3" s="16">
         <v>45817</v>
       </c>
-      <c r="Q3" s="19">
+      <c r="Q3" s="16">
         <v>45818</v>
       </c>
-      <c r="R3" s="19">
+      <c r="R3" s="16">
         <v>45819</v>
       </c>
-      <c r="S3" s="19">
+      <c r="S3" s="16">
         <v>45820</v>
       </c>
-      <c r="T3" s="19">
+      <c r="T3" s="16">
         <v>45821</v>
       </c>
-      <c r="U3" s="19">
+      <c r="U3" s="16">
         <v>45822</v>
       </c>
-      <c r="V3" s="19">
+      <c r="V3" s="16">
         <v>45823</v>
       </c>
-      <c r="W3" s="19">
+      <c r="W3" s="16">
         <v>45824</v>
       </c>
-      <c r="X3" s="19">
+      <c r="X3" s="16">
         <v>45825</v>
       </c>
-      <c r="Y3" s="19">
+      <c r="Y3" s="16">
         <v>45826</v>
       </c>
-      <c r="Z3" s="19">
+      <c r="Z3" s="16">
         <v>45827</v>
       </c>
-      <c r="AA3" s="19">
+      <c r="AA3" s="16">
         <v>45828</v>
       </c>
-      <c r="AB3" s="19">
+      <c r="AB3" s="16">
         <v>45829</v>
       </c>
-      <c r="AC3" s="19">
+      <c r="AC3" s="16">
         <v>45830</v>
       </c>
-      <c r="AD3" s="19">
+      <c r="AD3" s="16">
         <v>45831</v>
       </c>
-      <c r="AE3" s="19">
+      <c r="AE3" s="16">
         <v>45832</v>
       </c>
-      <c r="AF3" s="19">
+      <c r="AF3" s="16">
         <v>45833</v>
       </c>
-      <c r="AG3" s="19">
+      <c r="AG3" s="16">
         <v>45834</v>
       </c>
-      <c r="AH3" s="19">
+      <c r="AH3" s="16">
         <v>45835</v>
       </c>
-      <c r="AI3" s="19">
+      <c r="AI3" s="16">
         <v>45836</v>
       </c>
-      <c r="AJ3" s="19">
+      <c r="AJ3" s="16">
         <v>45837</v>
       </c>
-      <c r="AK3" s="19">
+      <c r="AK3" s="16">
         <v>45838</v>
       </c>
-      <c r="AL3" s="19">
+      <c r="AL3" s="16">
         <v>45839</v>
       </c>
-      <c r="AM3" s="19">
+      <c r="AM3" s="16">
         <v>45840</v>
       </c>
-      <c r="AN3" s="19">
+      <c r="AN3" s="16">
         <v>45841</v>
       </c>
-      <c r="AO3" s="19">
+      <c r="AO3" s="16">
         <v>45842</v>
       </c>
-      <c r="AP3" s="19">
+      <c r="AP3" s="16">
         <v>45843</v>
       </c>
-      <c r="AQ3" s="19">
+      <c r="AQ3" s="16">
         <v>45844</v>
       </c>
-      <c r="AR3" s="19">
+      <c r="AR3" s="16">
         <v>45845</v>
       </c>
-      <c r="AS3" s="19">
+      <c r="AS3" s="16">
         <v>45846</v>
       </c>
-      <c r="AT3" s="19">
+      <c r="AT3" s="16">
         <v>45847</v>
       </c>
-      <c r="AU3" s="19">
+      <c r="AU3" s="16">
         <v>45848</v>
       </c>
-      <c r="AV3" s="19">
+      <c r="AV3" s="16">
         <v>45849</v>
       </c>
-      <c r="AW3" s="19">
+      <c r="AW3" s="16">
         <v>45850</v>
       </c>
-      <c r="AX3" s="19">
+      <c r="AX3" s="16">
         <v>45851</v>
       </c>
-      <c r="AY3" s="19">
+      <c r="AY3" s="16">
         <v>45852</v>
       </c>
-      <c r="AZ3" s="19">
+      <c r="AZ3" s="16">
         <v>45853</v>
       </c>
-      <c r="BA3" s="19">
+      <c r="BA3" s="16">
         <v>45854</v>
       </c>
-      <c r="BB3" s="19">
+      <c r="BB3" s="16">
         <v>45855</v>
       </c>
-      <c r="BC3" s="19">
+      <c r="BC3" s="16">
         <v>45856</v>
       </c>
-      <c r="BD3" s="19">
+      <c r="BD3" s="16">
         <v>45857</v>
       </c>
-      <c r="BE3" s="19">
+      <c r="BE3" s="16">
         <v>45858</v>
       </c>
-      <c r="BF3" s="19">
+      <c r="BF3" s="16">
         <v>45859</v>
       </c>
-      <c r="BG3" s="19">
+      <c r="BG3" s="16">
         <v>45860</v>
       </c>
-      <c r="BH3" s="19">
+      <c r="BH3" s="16">
         <v>45861</v>
       </c>
-      <c r="BI3" s="19">
+      <c r="BI3" s="16">
         <v>45862</v>
       </c>
-      <c r="BJ3" s="19">
+      <c r="BJ3" s="16">
         <v>45863</v>
       </c>
-      <c r="BK3" s="19">
+      <c r="BK3" s="16">
         <v>45864</v>
       </c>
-      <c r="BL3" s="19">
+      <c r="BL3" s="16">
         <v>45865</v>
       </c>
-      <c r="BM3" s="19">
+      <c r="BM3" s="16">
         <v>45866</v>
       </c>
-      <c r="BN3" s="19">
+      <c r="BN3" s="16">
         <v>45867</v>
       </c>
-      <c r="BO3" s="19">
+      <c r="BO3" s="16">
         <v>45868</v>
       </c>
-      <c r="BP3" s="19">
+      <c r="BP3" s="16">
         <v>45869</v>
       </c>
-      <c r="BQ3" s="19">
+      <c r="BQ3" s="16">
         <v>45870</v>
       </c>
-      <c r="BR3" s="19">
+      <c r="BR3" s="16">
         <v>45871</v>
       </c>
-      <c r="BS3" s="19">
+      <c r="BS3" s="16">
         <v>45872</v>
       </c>
-      <c r="BT3" s="19">
+      <c r="BT3" s="16">
         <v>45873</v>
       </c>
-      <c r="BU3" s="19">
+      <c r="BU3" s="16">
         <v>45874</v>
       </c>
-      <c r="BV3" s="19">
+      <c r="BV3" s="16">
         <v>45875</v>
       </c>
-      <c r="BW3" s="19">
+      <c r="BW3" s="16">
         <v>45876</v>
       </c>
-      <c r="BX3" s="19">
+      <c r="BX3" s="16">
         <v>45877</v>
       </c>
-      <c r="BY3" s="19">
+      <c r="BY3" s="16">
         <v>45878</v>
       </c>
-      <c r="BZ3" s="19">
+      <c r="BZ3" s="16">
         <v>45879</v>
       </c>
+      <c r="CA3" s="38"/>
+      <c r="CB3" s="38"/>
+      <c r="CC3" s="38"/>
     </row>
-    <row r="4" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:81" ht="15.95" customHeight="1">
       <c r="A4" s="11" cm="1">
         <f t="array" ref="A4">IF($CC4="","",INDEX(Tasks!A$4:A$43,$CC4))</f>
         <v>1</v>
@@ -1730,23 +1743,23 @@
         <f t="array" ref="C4">IF($CC4="","",INDEX(Tasks!C$4:C$43,$CC4))</f>
         <v>Define scope &amp; goals</v>
       </c>
-      <c r="D4" s="20" t="str" cm="1">
+      <c r="D4" s="17" t="str" cm="1">
         <f t="array" ref="D4">IF($CC4="","",INDEX(Tasks!D$4:D$43,$CC4))</f>
         <v>John</v>
       </c>
-      <c r="E4" s="25" cm="1">
+      <c r="E4" s="20" cm="1">
         <f t="array" ref="E4">IF($CC4="","",INDEX(Tasks!E$4:E$43,$CC4))</f>
         <v>45810</v>
       </c>
-      <c r="F4" s="20" cm="1">
+      <c r="F4" s="17" cm="1">
         <f t="array" ref="F4">IF($CC4="","",INDEX(Tasks!F$4:F$43,$CC4))</f>
         <v>4</v>
       </c>
-      <c r="G4" s="25" cm="1">
+      <c r="G4" s="20" cm="1">
         <f t="array" ref="G4">IF($CC4="","",INDEX(Tasks!G$4:G$43,$CC4))</f>
         <v>45813</v>
       </c>
-      <c r="H4" s="21" cm="1">
+      <c r="H4" s="18" cm="1">
         <f t="array" ref="H4">IF($CC4="","",INDEX(Tasks!H$4:H$43,$CC4))</f>
         <v>1</v>
       </c>
@@ -2030,16 +2043,17 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="CB4" cm="1">
+      <c r="CA4" s="38"/>
+      <c r="CB4" s="38" cm="1">
         <f t="array" ref="CB4">IF(Tasks!C4="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E4)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E4)*(Tasks!$A$4:$A$43&lt;Tasks!A4)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v>1</v>
       </c>
-      <c r="CC4">
+      <c r="CC4" s="38">
         <f t="shared" ref="CC4:CC33" si="7">IFERROR(MATCH(ROW()-3,$CB$4:$CB$33,0),"")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:81" ht="15.95" customHeight="1">
       <c r="A5" s="11" cm="1">
         <f t="array" ref="A5">IF($CC5="","",INDEX(Tasks!A$4:A$43,$CC5))</f>
         <v>2</v>
@@ -2052,23 +2066,23 @@
         <f t="array" ref="C5">IF($CC5="","",INDEX(Tasks!C$4:C$43,$CC5))</f>
         <v>Stakeholder interviews</v>
       </c>
-      <c r="D5" s="20" t="str" cm="1">
+      <c r="D5" s="17" t="str" cm="1">
         <f t="array" ref="D5">IF($CC5="","",INDEX(Tasks!D$4:D$43,$CC5))</f>
         <v>John</v>
       </c>
-      <c r="E5" s="25" cm="1">
+      <c r="E5" s="20" cm="1">
         <f t="array" ref="E5">IF($CC5="","",INDEX(Tasks!E$4:E$43,$CC5))</f>
         <v>45811</v>
       </c>
-      <c r="F5" s="20" cm="1">
+      <c r="F5" s="17" cm="1">
         <f t="array" ref="F5">IF($CC5="","",INDEX(Tasks!F$4:F$43,$CC5))</f>
         <v>3</v>
       </c>
-      <c r="G5" s="25" cm="1">
+      <c r="G5" s="20" cm="1">
         <f t="array" ref="G5">IF($CC5="","",INDEX(Tasks!G$4:G$43,$CC5))</f>
         <v>45813</v>
       </c>
-      <c r="H5" s="21" cm="1">
+      <c r="H5" s="18" cm="1">
         <f t="array" ref="H5">IF($CC5="","",INDEX(Tasks!H$4:H$43,$CC5))</f>
         <v>1</v>
       </c>
@@ -2352,16 +2366,17 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="CB5" cm="1">
+      <c r="CA5" s="38"/>
+      <c r="CB5" s="38" cm="1">
         <f t="array" ref="CB5">IF(Tasks!C5="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E5)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E5)*(Tasks!$A$4:$A$43&lt;Tasks!A5)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v>2</v>
       </c>
-      <c r="CC5">
+      <c r="CC5" s="38">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:81" ht="15.95" customHeight="1">
       <c r="A6" s="11" cm="1">
         <f t="array" ref="A6">IF($CC6="","",INDEX(Tasks!A$4:A$43,$CC6))</f>
         <v>3</v>
@@ -2374,23 +2389,23 @@
         <f t="array" ref="C6">IF($CC6="","",INDEX(Tasks!C$4:C$43,$CC6))</f>
         <v>Requirements doc</v>
       </c>
-      <c r="D6" s="20" t="str" cm="1">
+      <c r="D6" s="17" t="str" cm="1">
         <f t="array" ref="D6">IF($CC6="","",INDEX(Tasks!D$4:D$43,$CC6))</f>
         <v>John</v>
       </c>
-      <c r="E6" s="25" cm="1">
+      <c r="E6" s="20" cm="1">
         <f t="array" ref="E6">IF($CC6="","",INDEX(Tasks!E$4:E$43,$CC6))</f>
         <v>45814</v>
       </c>
-      <c r="F6" s="20" cm="1">
+      <c r="F6" s="17" cm="1">
         <f t="array" ref="F6">IF($CC6="","",INDEX(Tasks!F$4:F$43,$CC6))</f>
         <v>5</v>
       </c>
-      <c r="G6" s="25" cm="1">
+      <c r="G6" s="20" cm="1">
         <f t="array" ref="G6">IF($CC6="","",INDEX(Tasks!G$4:G$43,$CC6))</f>
         <v>45818</v>
       </c>
-      <c r="H6" s="21" cm="1">
+      <c r="H6" s="18" cm="1">
         <f t="array" ref="H6">IF($CC6="","",INDEX(Tasks!H$4:H$43,$CC6))</f>
         <v>1</v>
       </c>
@@ -2674,16 +2689,17 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="CB6" cm="1">
+      <c r="CA6" s="38"/>
+      <c r="CB6" s="38" cm="1">
         <f t="array" ref="CB6">IF(Tasks!C6="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E6)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E6)*(Tasks!$A$4:$A$43&lt;Tasks!A6)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v>3</v>
       </c>
-      <c r="CC6">
+      <c r="CC6" s="38">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:81" ht="15.95" customHeight="1">
       <c r="A7" s="11" cm="1">
         <f t="array" ref="A7">IF($CC7="","",INDEX(Tasks!A$4:A$43,$CC7))</f>
         <v>4</v>
@@ -2696,23 +2712,23 @@
         <f t="array" ref="C7">IF($CC7="","",INDEX(Tasks!C$4:C$43,$CC7))</f>
         <v>Tech stack decision</v>
       </c>
-      <c r="D7" s="20" t="str" cm="1">
+      <c r="D7" s="17" t="str" cm="1">
         <f t="array" ref="D7">IF($CC7="","",INDEX(Tasks!D$4:D$43,$CC7))</f>
         <v>Jane</v>
       </c>
-      <c r="E7" s="25" cm="1">
+      <c r="E7" s="20" cm="1">
         <f t="array" ref="E7">IF($CC7="","",INDEX(Tasks!E$4:E$43,$CC7))</f>
         <v>45817</v>
       </c>
-      <c r="F7" s="20" cm="1">
+      <c r="F7" s="17" cm="1">
         <f t="array" ref="F7">IF($CC7="","",INDEX(Tasks!F$4:F$43,$CC7))</f>
         <v>3</v>
       </c>
-      <c r="G7" s="25" cm="1">
+      <c r="G7" s="20" cm="1">
         <f t="array" ref="G7">IF($CC7="","",INDEX(Tasks!G$4:G$43,$CC7))</f>
         <v>45819</v>
       </c>
-      <c r="H7" s="21" cm="1">
+      <c r="H7" s="18" cm="1">
         <f t="array" ref="H7">IF($CC7="","",INDEX(Tasks!H$4:H$43,$CC7))</f>
         <v>0.8</v>
       </c>
@@ -2996,16 +3012,17 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="CB7" cm="1">
+      <c r="CA7" s="38"/>
+      <c r="CB7" s="38" cm="1">
         <f t="array" ref="CB7">IF(Tasks!C7="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E7)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E7)*(Tasks!$A$4:$A$43&lt;Tasks!A7)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v>4</v>
       </c>
-      <c r="CC7">
+      <c r="CC7" s="38">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:81" ht="15.95" customHeight="1">
       <c r="A8" s="11" cm="1">
         <f t="array" ref="A8">IF($CC8="","",INDEX(Tasks!A$4:A$43,$CC8))</f>
         <v>5</v>
@@ -3018,23 +3035,23 @@
         <f t="array" ref="C8">IF($CC8="","",INDEX(Tasks!C$4:C$43,$CC8))</f>
         <v>UX wireframes</v>
       </c>
-      <c r="D8" s="20" t="str" cm="1">
+      <c r="D8" s="17" t="str" cm="1">
         <f t="array" ref="D8">IF($CC8="","",INDEX(Tasks!D$4:D$43,$CC8))</f>
         <v>Jane</v>
       </c>
-      <c r="E8" s="25" cm="1">
+      <c r="E8" s="20" cm="1">
         <f t="array" ref="E8">IF($CC8="","",INDEX(Tasks!E$4:E$43,$CC8))</f>
         <v>45820</v>
       </c>
-      <c r="F8" s="20" cm="1">
+      <c r="F8" s="17" cm="1">
         <f t="array" ref="F8">IF($CC8="","",INDEX(Tasks!F$4:F$43,$CC8))</f>
         <v>6</v>
       </c>
-      <c r="G8" s="25" cm="1">
+      <c r="G8" s="20" cm="1">
         <f t="array" ref="G8">IF($CC8="","",INDEX(Tasks!G$4:G$43,$CC8))</f>
         <v>45825</v>
       </c>
-      <c r="H8" s="21" cm="1">
+      <c r="H8" s="18" cm="1">
         <f t="array" ref="H8">IF($CC8="","",INDEX(Tasks!H$4:H$43,$CC8))</f>
         <v>0.6</v>
       </c>
@@ -3318,16 +3335,17 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="CB8" cm="1">
+      <c r="CA8" s="38"/>
+      <c r="CB8" s="38" cm="1">
         <f t="array" ref="CB8">IF(Tasks!C8="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E8)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E8)*(Tasks!$A$4:$A$43&lt;Tasks!A8)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v>5</v>
       </c>
-      <c r="CC8">
+      <c r="CC8" s="38">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:81" ht="15.95" customHeight="1">
       <c r="A9" s="11" cm="1">
         <f t="array" ref="A9">IF($CC9="","",INDEX(Tasks!A$4:A$43,$CC9))</f>
         <v>6</v>
@@ -3340,23 +3358,23 @@
         <f t="array" ref="C9">IF($CC9="","",INDEX(Tasks!C$4:C$43,$CC9))</f>
         <v>Design system / tokens</v>
       </c>
-      <c r="D9" s="20" t="str" cm="1">
+      <c r="D9" s="17" t="str" cm="1">
         <f t="array" ref="D9">IF($CC9="","",INDEX(Tasks!D$4:D$43,$CC9))</f>
         <v>Jane</v>
       </c>
-      <c r="E9" s="25" cm="1">
+      <c r="E9" s="20" cm="1">
         <f t="array" ref="E9">IF($CC9="","",INDEX(Tasks!E$4:E$43,$CC9))</f>
         <v>45824</v>
       </c>
-      <c r="F9" s="20" cm="1">
+      <c r="F9" s="17" cm="1">
         <f t="array" ref="F9">IF($CC9="","",INDEX(Tasks!F$4:F$43,$CC9))</f>
         <v>5</v>
       </c>
-      <c r="G9" s="25" cm="1">
+      <c r="G9" s="20" cm="1">
         <f t="array" ref="G9">IF($CC9="","",INDEX(Tasks!G$4:G$43,$CC9))</f>
         <v>45828</v>
       </c>
-      <c r="H9" s="21" cm="1">
+      <c r="H9" s="18" cm="1">
         <f t="array" ref="H9">IF($CC9="","",INDEX(Tasks!H$4:H$43,$CC9))</f>
         <v>0.2</v>
       </c>
@@ -3640,16 +3658,17 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="CB9" cm="1">
+      <c r="CA9" s="38"/>
+      <c r="CB9" s="38" cm="1">
         <f t="array" ref="CB9">IF(Tasks!C9="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E9)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E9)*(Tasks!$A$4:$A$43&lt;Tasks!A9)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v>6</v>
       </c>
-      <c r="CC9">
+      <c r="CC9" s="38">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:81" ht="15.95" customHeight="1">
       <c r="A10" s="11" cm="1">
         <f t="array" ref="A10">IF($CC10="","",INDEX(Tasks!A$4:A$43,$CC10))</f>
         <v>7</v>
@@ -3662,23 +3681,23 @@
         <f t="array" ref="C10">IF($CC10="","",INDEX(Tasks!C$4:C$43,$CC10))</f>
         <v>Prototype review</v>
       </c>
-      <c r="D10" s="20" t="str" cm="1">
+      <c r="D10" s="17" t="str" cm="1">
         <f t="array" ref="D10">IF($CC10="","",INDEX(Tasks!D$4:D$43,$CC10))</f>
         <v>John</v>
       </c>
-      <c r="E10" s="25" cm="1">
+      <c r="E10" s="20" cm="1">
         <f t="array" ref="E10">IF($CC10="","",INDEX(Tasks!E$4:E$43,$CC10))</f>
         <v>45826</v>
       </c>
-      <c r="F10" s="20" cm="1">
+      <c r="F10" s="17" cm="1">
         <f t="array" ref="F10">IF($CC10="","",INDEX(Tasks!F$4:F$43,$CC10))</f>
         <v>3</v>
       </c>
-      <c r="G10" s="25" cm="1">
+      <c r="G10" s="20" cm="1">
         <f t="array" ref="G10">IF($CC10="","",INDEX(Tasks!G$4:G$43,$CC10))</f>
         <v>45828</v>
       </c>
-      <c r="H10" s="21" cm="1">
+      <c r="H10" s="18" cm="1">
         <f t="array" ref="H10">IF($CC10="","",INDEX(Tasks!H$4:H$43,$CC10))</f>
         <v>0</v>
       </c>
@@ -3962,16 +3981,17 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="CB10" cm="1">
+      <c r="CA10" s="38"/>
+      <c r="CB10" s="38" cm="1">
         <f t="array" ref="CB10">IF(Tasks!C10="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E10)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E10)*(Tasks!$A$4:$A$43&lt;Tasks!A10)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v>7</v>
       </c>
-      <c r="CC10">
+      <c r="CC10" s="38">
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:81" ht="15.95" customHeight="1">
       <c r="A11" s="11" cm="1">
         <f t="array" ref="A11">IF($CC11="","",INDEX(Tasks!A$4:A$43,$CC11))</f>
         <v>8</v>
@@ -3984,23 +4004,23 @@
         <f t="array" ref="C11">IF($CC11="","",INDEX(Tasks!C$4:C$43,$CC11))</f>
         <v>Spreadsheet engine core</v>
       </c>
-      <c r="D11" s="20" t="str" cm="1">
+      <c r="D11" s="17" t="str" cm="1">
         <f t="array" ref="D11">IF($CC11="","",INDEX(Tasks!D$4:D$43,$CC11))</f>
         <v>Jane</v>
       </c>
-      <c r="E11" s="25" cm="1">
+      <c r="E11" s="20" cm="1">
         <f t="array" ref="E11">IF($CC11="","",INDEX(Tasks!E$4:E$43,$CC11))</f>
         <v>45829</v>
       </c>
-      <c r="F11" s="20" cm="1">
+      <c r="F11" s="17" cm="1">
         <f t="array" ref="F11">IF($CC11="","",INDEX(Tasks!F$4:F$43,$CC11))</f>
         <v>14</v>
       </c>
-      <c r="G11" s="25" cm="1">
+      <c r="G11" s="20" cm="1">
         <f t="array" ref="G11">IF($CC11="","",INDEX(Tasks!G$4:G$43,$CC11))</f>
         <v>45842</v>
       </c>
-      <c r="H11" s="21" cm="1">
+      <c r="H11" s="18" cm="1">
         <f t="array" ref="H11">IF($CC11="","",INDEX(Tasks!H$4:H$43,$CC11))</f>
         <v>0</v>
       </c>
@@ -4284,16 +4304,17 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="CB11" cm="1">
+      <c r="CA11" s="38"/>
+      <c r="CB11" s="38" cm="1">
         <f t="array" ref="CB11">IF(Tasks!C11="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E11)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E11)*(Tasks!$A$4:$A$43&lt;Tasks!A11)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v>8</v>
       </c>
-      <c r="CC11">
+      <c r="CC11" s="38">
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:81" ht="15.95" customHeight="1">
       <c r="A12" s="11" cm="1">
         <f t="array" ref="A12">IF($CC12="","",INDEX(Tasks!A$4:A$43,$CC12))</f>
         <v>10</v>
@@ -4306,23 +4327,23 @@
         <f t="array" ref="C12">IF($CC12="","",INDEX(Tasks!C$4:C$43,$CC12))</f>
         <v>Frontend components</v>
       </c>
-      <c r="D12" s="20" t="str" cm="1">
+      <c r="D12" s="17" t="str" cm="1">
         <f t="array" ref="D12">IF($CC12="","",INDEX(Tasks!D$4:D$43,$CC12))</f>
         <v>John</v>
       </c>
-      <c r="E12" s="25" cm="1">
+      <c r="E12" s="20" cm="1">
         <f t="array" ref="E12">IF($CC12="","",INDEX(Tasks!E$4:E$43,$CC12))</f>
         <v>45829</v>
       </c>
-      <c r="F12" s="20" cm="1">
+      <c r="F12" s="17" cm="1">
         <f t="array" ref="F12">IF($CC12="","",INDEX(Tasks!F$4:F$43,$CC12))</f>
         <v>12</v>
       </c>
-      <c r="G12" s="25" cm="1">
+      <c r="G12" s="20" cm="1">
         <f t="array" ref="G12">IF($CC12="","",INDEX(Tasks!G$4:G$43,$CC12))</f>
         <v>45840</v>
       </c>
-      <c r="H12" s="21" cm="1">
+      <c r="H12" s="18" cm="1">
         <f t="array" ref="H12">IF($CC12="","",INDEX(Tasks!H$4:H$43,$CC12))</f>
         <v>0</v>
       </c>
@@ -4606,16 +4627,17 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="CB12" cm="1">
+      <c r="CA12" s="38"/>
+      <c r="CB12" s="38" cm="1">
         <f t="array" ref="CB12">IF(Tasks!C12="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E12)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E12)*(Tasks!$A$4:$A$43&lt;Tasks!A12)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v>10</v>
       </c>
-      <c r="CC12">
+      <c r="CC12" s="38">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:81" ht="15.95" customHeight="1">
       <c r="A13" s="11" cm="1">
         <f t="array" ref="A13">IF($CC13="","",INDEX(Tasks!A$4:A$43,$CC13))</f>
         <v>9</v>
@@ -4628,23 +4650,23 @@
         <f t="array" ref="C13">IF($CC13="","",INDEX(Tasks!C$4:C$43,$CC13))</f>
         <v>Formula parser v2</v>
       </c>
-      <c r="D13" s="20" t="str" cm="1">
+      <c r="D13" s="17" t="str" cm="1">
         <f t="array" ref="D13">IF($CC13="","",INDEX(Tasks!D$4:D$43,$CC13))</f>
         <v>Jane</v>
       </c>
-      <c r="E13" s="25" cm="1">
+      <c r="E13" s="20" cm="1">
         <f t="array" ref="E13">IF($CC13="","",INDEX(Tasks!E$4:E$43,$CC13))</f>
         <v>45832</v>
       </c>
-      <c r="F13" s="20" cm="1">
+      <c r="F13" s="17" cm="1">
         <f t="array" ref="F13">IF($CC13="","",INDEX(Tasks!F$4:F$43,$CC13))</f>
         <v>10</v>
       </c>
-      <c r="G13" s="25" cm="1">
+      <c r="G13" s="20" cm="1">
         <f t="array" ref="G13">IF($CC13="","",INDEX(Tasks!G$4:G$43,$CC13))</f>
         <v>45841</v>
       </c>
-      <c r="H13" s="21" cm="1">
+      <c r="H13" s="18" cm="1">
         <f t="array" ref="H13">IF($CC13="","",INDEX(Tasks!H$4:H$43,$CC13))</f>
         <v>0</v>
       </c>
@@ -4928,16 +4950,17 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="CB13" cm="1">
+      <c r="CA13" s="38"/>
+      <c r="CB13" s="38" cm="1">
         <f t="array" ref="CB13">IF(Tasks!C13="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E13)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E13)*(Tasks!$A$4:$A$43&lt;Tasks!A13)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v>9</v>
       </c>
-      <c r="CC13">
+      <c r="CC13" s="38">
         <f t="shared" si="7"/>
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:81" ht="15.95" customHeight="1">
       <c r="A14" s="11" cm="1">
         <f t="array" ref="A14">IF($CC14="","",INDEX(Tasks!A$4:A$43,$CC14))</f>
         <v>11</v>
@@ -4950,23 +4973,23 @@
         <f t="array" ref="C14">IF($CC14="","",INDEX(Tasks!C$4:C$43,$CC14))</f>
         <v>WebAssembly build</v>
       </c>
-      <c r="D14" s="20" t="str" cm="1">
+      <c r="D14" s="17" t="str" cm="1">
         <f t="array" ref="D14">IF($CC14="","",INDEX(Tasks!D$4:D$43,$CC14))</f>
         <v>John</v>
       </c>
-      <c r="E14" s="25" cm="1">
+      <c r="E14" s="20" cm="1">
         <f t="array" ref="E14">IF($CC14="","",INDEX(Tasks!E$4:E$43,$CC14))</f>
         <v>45840</v>
       </c>
-      <c r="F14" s="20" cm="1">
+      <c r="F14" s="17" cm="1">
         <f t="array" ref="F14">IF($CC14="","",INDEX(Tasks!F$4:F$43,$CC14))</f>
         <v>8</v>
       </c>
-      <c r="G14" s="25" cm="1">
+      <c r="G14" s="20" cm="1">
         <f t="array" ref="G14">IF($CC14="","",INDEX(Tasks!G$4:G$43,$CC14))</f>
         <v>45847</v>
       </c>
-      <c r="H14" s="21" cm="1">
+      <c r="H14" s="18" cm="1">
         <f t="array" ref="H14">IF($CC14="","",INDEX(Tasks!H$4:H$43,$CC14))</f>
         <v>0</v>
       </c>
@@ -5250,16 +5273,17 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="CB14" cm="1">
+      <c r="CA14" s="38"/>
+      <c r="CB14" s="38" cm="1">
         <f t="array" ref="CB14">IF(Tasks!C14="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E14)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E14)*(Tasks!$A$4:$A$43&lt;Tasks!A14)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v>11</v>
       </c>
-      <c r="CC14">
+      <c r="CC14" s="38">
         <f t="shared" si="7"/>
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:81" ht="15.95" customHeight="1">
       <c r="A15" s="11" cm="1">
         <f t="array" ref="A15">IF($CC15="","",INDEX(Tasks!A$4:A$43,$CC15))</f>
         <v>12</v>
@@ -5272,23 +5296,23 @@
         <f t="array" ref="C15">IF($CC15="","",INDEX(Tasks!C$4:C$43,$CC15))</f>
         <v>API integration</v>
       </c>
-      <c r="D15" s="20" t="str" cm="1">
+      <c r="D15" s="17" t="str" cm="1">
         <f t="array" ref="D15">IF($CC15="","",INDEX(Tasks!D$4:D$43,$CC15))</f>
         <v>Jane</v>
       </c>
-      <c r="E15" s="25" cm="1">
+      <c r="E15" s="20" cm="1">
         <f t="array" ref="E15">IF($CC15="","",INDEX(Tasks!E$4:E$43,$CC15))</f>
         <v>45841</v>
       </c>
-      <c r="F15" s="20" cm="1">
+      <c r="F15" s="17" cm="1">
         <f t="array" ref="F15">IF($CC15="","",INDEX(Tasks!F$4:F$43,$CC15))</f>
         <v>10</v>
       </c>
-      <c r="G15" s="25" cm="1">
+      <c r="G15" s="20" cm="1">
         <f t="array" ref="G15">IF($CC15="","",INDEX(Tasks!G$4:G$43,$CC15))</f>
         <v>45850</v>
       </c>
-      <c r="H15" s="21" cm="1">
+      <c r="H15" s="18" cm="1">
         <f t="array" ref="H15">IF($CC15="","",INDEX(Tasks!H$4:H$43,$CC15))</f>
         <v>0</v>
       </c>
@@ -5572,16 +5596,17 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="CB15" cm="1">
+      <c r="CA15" s="38"/>
+      <c r="CB15" s="38" cm="1">
         <f t="array" ref="CB15">IF(Tasks!C15="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E15)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E15)*(Tasks!$A$4:$A$43&lt;Tasks!A15)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v>12</v>
       </c>
-      <c r="CC15">
+      <c r="CC15" s="38">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:81" ht="15.95" customHeight="1">
       <c r="A16" s="11" cm="1">
         <f t="array" ref="A16">IF($CC16="","",INDEX(Tasks!A$4:A$43,$CC16))</f>
         <v>13</v>
@@ -5594,23 +5619,23 @@
         <f t="array" ref="C16">IF($CC16="","",INDEX(Tasks!C$4:C$43,$CC16))</f>
         <v>Unit test suite</v>
       </c>
-      <c r="D16" s="20" t="str" cm="1">
+      <c r="D16" s="17" t="str" cm="1">
         <f t="array" ref="D16">IF($CC16="","",INDEX(Tasks!D$4:D$43,$CC16))</f>
         <v>John</v>
       </c>
-      <c r="E16" s="25" cm="1">
+      <c r="E16" s="20" cm="1">
         <f t="array" ref="E16">IF($CC16="","",INDEX(Tasks!E$4:E$43,$CC16))</f>
         <v>45850</v>
       </c>
-      <c r="F16" s="20" cm="1">
+      <c r="F16" s="17" cm="1">
         <f t="array" ref="F16">IF($CC16="","",INDEX(Tasks!F$4:F$43,$CC16))</f>
         <v>6</v>
       </c>
-      <c r="G16" s="25" cm="1">
+      <c r="G16" s="20" cm="1">
         <f t="array" ref="G16">IF($CC16="","",INDEX(Tasks!G$4:G$43,$CC16))</f>
         <v>45855</v>
       </c>
-      <c r="H16" s="21" cm="1">
+      <c r="H16" s="18" cm="1">
         <f t="array" ref="H16">IF($CC16="","",INDEX(Tasks!H$4:H$43,$CC16))</f>
         <v>0</v>
       </c>
@@ -5894,16 +5919,17 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="CB16" cm="1">
+      <c r="CA16" s="38"/>
+      <c r="CB16" s="38" cm="1">
         <f t="array" ref="CB16">IF(Tasks!C16="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E16)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E16)*(Tasks!$A$4:$A$43&lt;Tasks!A16)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v>13</v>
       </c>
-      <c r="CC16">
+      <c r="CC16" s="38">
         <f t="shared" si="7"/>
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:81" ht="15.95" customHeight="1">
       <c r="A17" s="11" cm="1">
         <f t="array" ref="A17">IF($CC17="","",INDEX(Tasks!A$4:A$43,$CC17))</f>
         <v>14</v>
@@ -5916,23 +5942,23 @@
         <f t="array" ref="C17">IF($CC17="","",INDEX(Tasks!C$4:C$43,$CC17))</f>
         <v>Cross-browser QA</v>
       </c>
-      <c r="D17" s="20" t="str" cm="1">
+      <c r="D17" s="17" t="str" cm="1">
         <f t="array" ref="D17">IF($CC17="","",INDEX(Tasks!D$4:D$43,$CC17))</f>
         <v>Jane</v>
       </c>
-      <c r="E17" s="25" cm="1">
+      <c r="E17" s="20" cm="1">
         <f t="array" ref="E17">IF($CC17="","",INDEX(Tasks!E$4:E$43,$CC17))</f>
         <v>45854</v>
       </c>
-      <c r="F17" s="20" cm="1">
+      <c r="F17" s="17" cm="1">
         <f t="array" ref="F17">IF($CC17="","",INDEX(Tasks!F$4:F$43,$CC17))</f>
         <v>5</v>
       </c>
-      <c r="G17" s="25" cm="1">
+      <c r="G17" s="20" cm="1">
         <f t="array" ref="G17">IF($CC17="","",INDEX(Tasks!G$4:G$43,$CC17))</f>
         <v>45858</v>
       </c>
-      <c r="H17" s="21" cm="1">
+      <c r="H17" s="18" cm="1">
         <f t="array" ref="H17">IF($CC17="","",INDEX(Tasks!H$4:H$43,$CC17))</f>
         <v>0</v>
       </c>
@@ -6216,16 +6242,17 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="CB17" cm="1">
+      <c r="CA17" s="38"/>
+      <c r="CB17" s="38" cm="1">
         <f t="array" ref="CB17">IF(Tasks!C17="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E17)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E17)*(Tasks!$A$4:$A$43&lt;Tasks!A17)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v>14</v>
       </c>
-      <c r="CC17">
+      <c r="CC17" s="38">
         <f t="shared" si="7"/>
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:81" ht="15.95" customHeight="1">
       <c r="A18" s="11" cm="1">
         <f t="array" ref="A18">IF($CC18="","",INDEX(Tasks!A$4:A$43,$CC18))</f>
         <v>15</v>
@@ -6238,23 +6265,23 @@
         <f t="array" ref="C18">IF($CC18="","",INDEX(Tasks!C$4:C$43,$CC18))</f>
         <v>Performance benchmarks</v>
       </c>
-      <c r="D18" s="20" t="str" cm="1">
+      <c r="D18" s="17" t="str" cm="1">
         <f t="array" ref="D18">IF($CC18="","",INDEX(Tasks!D$4:D$43,$CC18))</f>
         <v>Jane</v>
       </c>
-      <c r="E18" s="25" cm="1">
+      <c r="E18" s="20" cm="1">
         <f t="array" ref="E18">IF($CC18="","",INDEX(Tasks!E$4:E$43,$CC18))</f>
         <v>45856</v>
       </c>
-      <c r="F18" s="20" cm="1">
+      <c r="F18" s="17" cm="1">
         <f t="array" ref="F18">IF($CC18="","",INDEX(Tasks!F$4:F$43,$CC18))</f>
         <v>5</v>
       </c>
-      <c r="G18" s="25" cm="1">
+      <c r="G18" s="20" cm="1">
         <f t="array" ref="G18">IF($CC18="","",INDEX(Tasks!G$4:G$43,$CC18))</f>
         <v>45860</v>
       </c>
-      <c r="H18" s="21" cm="1">
+      <c r="H18" s="18" cm="1">
         <f t="array" ref="H18">IF($CC18="","",INDEX(Tasks!H$4:H$43,$CC18))</f>
         <v>0</v>
       </c>
@@ -6538,16 +6565,17 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="CB18" cm="1">
+      <c r="CA18" s="38"/>
+      <c r="CB18" s="38" cm="1">
         <f t="array" ref="CB18">IF(Tasks!C18="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E18)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E18)*(Tasks!$A$4:$A$43&lt;Tasks!A18)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v>15</v>
       </c>
-      <c r="CC18">
+      <c r="CC18" s="38">
         <f t="shared" si="7"/>
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:81" ht="15.95" customHeight="1">
       <c r="A19" s="11" cm="1">
         <f t="array" ref="A19">IF($CC19="","",INDEX(Tasks!A$4:A$43,$CC19))</f>
         <v>16</v>
@@ -6560,23 +6588,23 @@
         <f t="array" ref="C19">IF($CC19="","",INDEX(Tasks!C$4:C$43,$CC19))</f>
         <v>Bug fixes</v>
       </c>
-      <c r="D19" s="20" t="str" cm="1">
+      <c r="D19" s="17" t="str" cm="1">
         <f t="array" ref="D19">IF($CC19="","",INDEX(Tasks!D$4:D$43,$CC19))</f>
         <v>John</v>
       </c>
-      <c r="E19" s="25" cm="1">
+      <c r="E19" s="20" cm="1">
         <f t="array" ref="E19">IF($CC19="","",INDEX(Tasks!E$4:E$43,$CC19))</f>
         <v>45858</v>
       </c>
-      <c r="F19" s="20" cm="1">
+      <c r="F19" s="17" cm="1">
         <f t="array" ref="F19">IF($CC19="","",INDEX(Tasks!F$4:F$43,$CC19))</f>
         <v>5</v>
       </c>
-      <c r="G19" s="25" cm="1">
+      <c r="G19" s="20" cm="1">
         <f t="array" ref="G19">IF($CC19="","",INDEX(Tasks!G$4:G$43,$CC19))</f>
         <v>45862</v>
       </c>
-      <c r="H19" s="21" cm="1">
+      <c r="H19" s="18" cm="1">
         <f t="array" ref="H19">IF($CC19="","",INDEX(Tasks!H$4:H$43,$CC19))</f>
         <v>0</v>
       </c>
@@ -6860,16 +6888,17 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="CB19" cm="1">
+      <c r="CA19" s="38"/>
+      <c r="CB19" s="38" cm="1">
         <f t="array" ref="CB19">IF(Tasks!C19="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E19)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E19)*(Tasks!$A$4:$A$43&lt;Tasks!A19)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v>16</v>
       </c>
-      <c r="CC19">
+      <c r="CC19" s="38">
         <f t="shared" si="7"/>
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:81" ht="15.95" customHeight="1">
       <c r="A20" s="11" cm="1">
         <f t="array" ref="A20">IF($CC20="","",INDEX(Tasks!A$4:A$43,$CC20))</f>
         <v>17</v>
@@ -6882,23 +6911,23 @@
         <f t="array" ref="C20">IF($CC20="","",INDEX(Tasks!C$4:C$43,$CC20))</f>
         <v>Docs &amp; changelog</v>
       </c>
-      <c r="D20" s="20" t="str" cm="1">
+      <c r="D20" s="17" t="str" cm="1">
         <f t="array" ref="D20">IF($CC20="","",INDEX(Tasks!D$4:D$43,$CC20))</f>
         <v>John</v>
       </c>
-      <c r="E20" s="25" cm="1">
+      <c r="E20" s="20" cm="1">
         <f t="array" ref="E20">IF($CC20="","",INDEX(Tasks!E$4:E$43,$CC20))</f>
         <v>45864</v>
       </c>
-      <c r="F20" s="20" cm="1">
+      <c r="F20" s="17" cm="1">
         <f t="array" ref="F20">IF($CC20="","",INDEX(Tasks!F$4:F$43,$CC20))</f>
         <v>4</v>
       </c>
-      <c r="G20" s="25" cm="1">
+      <c r="G20" s="20" cm="1">
         <f t="array" ref="G20">IF($CC20="","",INDEX(Tasks!G$4:G$43,$CC20))</f>
         <v>45867</v>
       </c>
-      <c r="H20" s="21" cm="1">
+      <c r="H20" s="18" cm="1">
         <f t="array" ref="H20">IF($CC20="","",INDEX(Tasks!H$4:H$43,$CC20))</f>
         <v>0</v>
       </c>
@@ -7182,16 +7211,17 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="CB20" cm="1">
+      <c r="CA20" s="38"/>
+      <c r="CB20" s="38" cm="1">
         <f t="array" ref="CB20">IF(Tasks!C20="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E20)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E20)*(Tasks!$A$4:$A$43&lt;Tasks!A20)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v>17</v>
       </c>
-      <c r="CC20">
+      <c r="CC20" s="38">
         <f t="shared" si="7"/>
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:81" ht="15.95" customHeight="1">
       <c r="A21" s="11" cm="1">
         <f t="array" ref="A21">IF($CC21="","",INDEX(Tasks!A$4:A$43,$CC21))</f>
         <v>18</v>
@@ -7204,23 +7234,23 @@
         <f t="array" ref="C21">IF($CC21="","",INDEX(Tasks!C$4:C$43,$CC21))</f>
         <v>Beta release</v>
       </c>
-      <c r="D21" s="20" t="str" cm="1">
+      <c r="D21" s="17" t="str" cm="1">
         <f t="array" ref="D21">IF($CC21="","",INDEX(Tasks!D$4:D$43,$CC21))</f>
         <v>Jane</v>
       </c>
-      <c r="E21" s="25" cm="1">
+      <c r="E21" s="20" cm="1">
         <f t="array" ref="E21">IF($CC21="","",INDEX(Tasks!E$4:E$43,$CC21))</f>
         <v>45867</v>
       </c>
-      <c r="F21" s="20" cm="1">
+      <c r="F21" s="17" cm="1">
         <f t="array" ref="F21">IF($CC21="","",INDEX(Tasks!F$4:F$43,$CC21))</f>
         <v>3</v>
       </c>
-      <c r="G21" s="25" cm="1">
+      <c r="G21" s="20" cm="1">
         <f t="array" ref="G21">IF($CC21="","",INDEX(Tasks!G$4:G$43,$CC21))</f>
         <v>45869</v>
       </c>
-      <c r="H21" s="21" cm="1">
+      <c r="H21" s="18" cm="1">
         <f t="array" ref="H21">IF($CC21="","",INDEX(Tasks!H$4:H$43,$CC21))</f>
         <v>0</v>
       </c>
@@ -7504,16 +7534,17 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="CB21" cm="1">
+      <c r="CA21" s="38"/>
+      <c r="CB21" s="38" cm="1">
         <f t="array" ref="CB21">IF(Tasks!C21="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E21)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E21)*(Tasks!$A$4:$A$43&lt;Tasks!A21)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v>18</v>
       </c>
-      <c r="CC21">
+      <c r="CC21" s="38">
         <f t="shared" si="7"/>
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:81" ht="15.95" customHeight="1">
       <c r="A22" s="11" cm="1">
         <f t="array" ref="A22">IF($CC22="","",INDEX(Tasks!A$4:A$43,$CC22))</f>
         <v>19</v>
@@ -7526,23 +7557,23 @@
         <f t="array" ref="C22">IF($CC22="","",INDEX(Tasks!C$4:C$43,$CC22))</f>
         <v>Marketing page</v>
       </c>
-      <c r="D22" s="20" t="str" cm="1">
+      <c r="D22" s="17" t="str" cm="1">
         <f t="array" ref="D22">IF($CC22="","",INDEX(Tasks!D$4:D$43,$CC22))</f>
         <v>Jane</v>
       </c>
-      <c r="E22" s="25" cm="1">
+      <c r="E22" s="20" cm="1">
         <f t="array" ref="E22">IF($CC22="","",INDEX(Tasks!E$4:E$43,$CC22))</f>
         <v>45868</v>
       </c>
-      <c r="F22" s="20" cm="1">
+      <c r="F22" s="17" cm="1">
         <f t="array" ref="F22">IF($CC22="","",INDEX(Tasks!F$4:F$43,$CC22))</f>
         <v>5</v>
       </c>
-      <c r="G22" s="25" cm="1">
+      <c r="G22" s="20" cm="1">
         <f t="array" ref="G22">IF($CC22="","",INDEX(Tasks!G$4:G$43,$CC22))</f>
         <v>45872</v>
       </c>
-      <c r="H22" s="21" cm="1">
+      <c r="H22" s="18" cm="1">
         <f t="array" ref="H22">IF($CC22="","",INDEX(Tasks!H$4:H$43,$CC22))</f>
         <v>0</v>
       </c>
@@ -7826,16 +7857,17 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="CB22" cm="1">
+      <c r="CA22" s="38"/>
+      <c r="CB22" s="38" cm="1">
         <f t="array" ref="CB22">IF(Tasks!C22="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E22)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E22)*(Tasks!$A$4:$A$43&lt;Tasks!A22)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v>19</v>
       </c>
-      <c r="CC22">
+      <c r="CC22" s="38">
         <f t="shared" si="7"/>
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:81" ht="15.95" customHeight="1">
       <c r="A23" s="11" cm="1">
         <f t="array" ref="A23">IF($CC23="","",INDEX(Tasks!A$4:A$43,$CC23))</f>
         <v>20</v>
@@ -7848,23 +7880,23 @@
         <f t="array" ref="C23">IF($CC23="","",INDEX(Tasks!C$4:C$43,$CC23))</f>
         <v>v1.0 release 🚀</v>
       </c>
-      <c r="D23" s="20" t="str" cm="1">
+      <c r="D23" s="17" t="str" cm="1">
         <f t="array" ref="D23">IF($CC23="","",INDEX(Tasks!D$4:D$43,$CC23))</f>
         <v>John</v>
       </c>
-      <c r="E23" s="25" cm="1">
+      <c r="E23" s="20" cm="1">
         <f t="array" ref="E23">IF($CC23="","",INDEX(Tasks!E$4:E$43,$CC23))</f>
         <v>45873</v>
       </c>
-      <c r="F23" s="20" cm="1">
+      <c r="F23" s="17" cm="1">
         <f t="array" ref="F23">IF($CC23="","",INDEX(Tasks!F$4:F$43,$CC23))</f>
         <v>2</v>
       </c>
-      <c r="G23" s="25" cm="1">
+      <c r="G23" s="20" cm="1">
         <f t="array" ref="G23">IF($CC23="","",INDEX(Tasks!G$4:G$43,$CC23))</f>
         <v>45874</v>
       </c>
-      <c r="H23" s="21" cm="1">
+      <c r="H23" s="18" cm="1">
         <f t="array" ref="H23">IF($CC23="","",INDEX(Tasks!H$4:H$43,$CC23))</f>
         <v>0</v>
       </c>
@@ -8148,45 +8180,46 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="CB23" cm="1">
+      <c r="CA23" s="38"/>
+      <c r="CB23" s="38" cm="1">
         <f t="array" ref="CB23">IF(Tasks!C23="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E23)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E23)*(Tasks!$A$4:$A$43&lt;Tasks!A23)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v>20</v>
       </c>
-      <c r="CC23">
+      <c r="CC23" s="38">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="14" t="str" cm="1">
+    <row r="24" spans="1:81" ht="15.95" customHeight="1">
+      <c r="A24" s="32" t="str" cm="1">
         <f t="array" ref="A24">IF($CC24="","",INDEX(Tasks!A$4:A$43,$CC24))</f>
         <v/>
       </c>
-      <c r="B24" s="15" t="str" cm="1">
+      <c r="B24" s="33" t="str" cm="1">
         <f t="array" ref="B24">IF($CC24="","",INDEX(Tasks!B$4:B$43,$CC24))</f>
         <v/>
       </c>
-      <c r="C24" s="16" t="str" cm="1">
+      <c r="C24" s="34" t="str" cm="1">
         <f t="array" ref="C24">IF($CC24="","",INDEX(Tasks!C$4:C$43,$CC24))</f>
         <v/>
       </c>
-      <c r="D24" s="22" t="str" cm="1">
+      <c r="D24" s="35" t="str" cm="1">
         <f t="array" ref="D24">IF($CC24="","",INDEX(Tasks!D$4:D$43,$CC24))</f>
         <v/>
       </c>
-      <c r="E24" s="31" t="str" cm="1">
+      <c r="E24" s="36" t="str" cm="1">
         <f t="array" ref="E24">IF($CC24="","",INDEX(Tasks!E$4:E$43,$CC24))</f>
         <v/>
       </c>
-      <c r="F24" s="22" t="str" cm="1">
+      <c r="F24" s="35" t="str" cm="1">
         <f t="array" ref="F24">IF($CC24="","",INDEX(Tasks!F$4:F$43,$CC24))</f>
         <v/>
       </c>
-      <c r="G24" s="31" t="str" cm="1">
+      <c r="G24" s="36" t="str" cm="1">
         <f t="array" ref="G24">IF($CC24="","",INDEX(Tasks!G$4:G$43,$CC24))</f>
         <v/>
       </c>
-      <c r="H24" s="23" t="str" cm="1">
+      <c r="H24" s="37" t="str" cm="1">
         <f t="array" ref="H24">IF($CC24="","",INDEX(Tasks!H$4:H$43,$CC24))</f>
         <v/>
       </c>
@@ -8470,45 +8503,46 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="CB24" t="str" cm="1">
+      <c r="CA24" s="38"/>
+      <c r="CB24" s="38" t="str" cm="1">
         <f t="array" ref="CB24">IF(Tasks!C24="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E24)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E24)*(Tasks!$A$4:$A$43&lt;Tasks!A24)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v/>
       </c>
-      <c r="CC24" t="str">
+      <c r="CC24" s="38" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="14" t="str" cm="1">
+    <row r="25" spans="1:81" ht="15.95" customHeight="1">
+      <c r="A25" s="32" t="str" cm="1">
         <f t="array" ref="A25">IF($CC25="","",INDEX(Tasks!A$4:A$43,$CC25))</f>
         <v/>
       </c>
-      <c r="B25" s="15" t="str" cm="1">
+      <c r="B25" s="33" t="str" cm="1">
         <f t="array" ref="B25">IF($CC25="","",INDEX(Tasks!B$4:B$43,$CC25))</f>
         <v/>
       </c>
-      <c r="C25" s="16" t="str" cm="1">
+      <c r="C25" s="34" t="str" cm="1">
         <f t="array" ref="C25">IF($CC25="","",INDEX(Tasks!C$4:C$43,$CC25))</f>
         <v/>
       </c>
-      <c r="D25" s="22" t="str" cm="1">
+      <c r="D25" s="35" t="str" cm="1">
         <f t="array" ref="D25">IF($CC25="","",INDEX(Tasks!D$4:D$43,$CC25))</f>
         <v/>
       </c>
-      <c r="E25" s="31" t="str" cm="1">
+      <c r="E25" s="36" t="str" cm="1">
         <f t="array" ref="E25">IF($CC25="","",INDEX(Tasks!E$4:E$43,$CC25))</f>
         <v/>
       </c>
-      <c r="F25" s="22" t="str" cm="1">
+      <c r="F25" s="35" t="str" cm="1">
         <f t="array" ref="F25">IF($CC25="","",INDEX(Tasks!F$4:F$43,$CC25))</f>
         <v/>
       </c>
-      <c r="G25" s="31" t="str" cm="1">
+      <c r="G25" s="36" t="str" cm="1">
         <f t="array" ref="G25">IF($CC25="","",INDEX(Tasks!G$4:G$43,$CC25))</f>
         <v/>
       </c>
-      <c r="H25" s="23" t="str" cm="1">
+      <c r="H25" s="37" t="str" cm="1">
         <f t="array" ref="H25">IF($CC25="","",INDEX(Tasks!H$4:H$43,$CC25))</f>
         <v/>
       </c>
@@ -8792,45 +8826,46 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="CB25" t="str" cm="1">
+      <c r="CA25" s="38"/>
+      <c r="CB25" s="38" t="str" cm="1">
         <f t="array" ref="CB25">IF(Tasks!C25="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E25)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E25)*(Tasks!$A$4:$A$43&lt;Tasks!A25)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v/>
       </c>
-      <c r="CC25" t="str">
+      <c r="CC25" s="38" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="14" t="str" cm="1">
+    <row r="26" spans="1:81" ht="15.95" customHeight="1">
+      <c r="A26" s="32" t="str" cm="1">
         <f t="array" ref="A26">IF($CC26="","",INDEX(Tasks!A$4:A$43,$CC26))</f>
         <v/>
       </c>
-      <c r="B26" s="15" t="str" cm="1">
+      <c r="B26" s="33" t="str" cm="1">
         <f t="array" ref="B26">IF($CC26="","",INDEX(Tasks!B$4:B$43,$CC26))</f>
         <v/>
       </c>
-      <c r="C26" s="16" t="str" cm="1">
+      <c r="C26" s="34" t="str" cm="1">
         <f t="array" ref="C26">IF($CC26="","",INDEX(Tasks!C$4:C$43,$CC26))</f>
         <v/>
       </c>
-      <c r="D26" s="22" t="str" cm="1">
+      <c r="D26" s="35" t="str" cm="1">
         <f t="array" ref="D26">IF($CC26="","",INDEX(Tasks!D$4:D$43,$CC26))</f>
         <v/>
       </c>
-      <c r="E26" s="31" t="str" cm="1">
+      <c r="E26" s="36" t="str" cm="1">
         <f t="array" ref="E26">IF($CC26="","",INDEX(Tasks!E$4:E$43,$CC26))</f>
         <v/>
       </c>
-      <c r="F26" s="22" t="str" cm="1">
+      <c r="F26" s="35" t="str" cm="1">
         <f t="array" ref="F26">IF($CC26="","",INDEX(Tasks!F$4:F$43,$CC26))</f>
         <v/>
       </c>
-      <c r="G26" s="31" t="str" cm="1">
+      <c r="G26" s="36" t="str" cm="1">
         <f t="array" ref="G26">IF($CC26="","",INDEX(Tasks!G$4:G$43,$CC26))</f>
         <v/>
       </c>
-      <c r="H26" s="23" t="str" cm="1">
+      <c r="H26" s="37" t="str" cm="1">
         <f t="array" ref="H26">IF($CC26="","",INDEX(Tasks!H$4:H$43,$CC26))</f>
         <v/>
       </c>
@@ -9114,45 +9149,46 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="CB26" t="str" cm="1">
+      <c r="CA26" s="38"/>
+      <c r="CB26" s="38" t="str" cm="1">
         <f t="array" ref="CB26">IF(Tasks!C26="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E26)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E26)*(Tasks!$A$4:$A$43&lt;Tasks!A26)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v/>
       </c>
-      <c r="CC26" t="str">
+      <c r="CC26" s="38" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="14" t="str" cm="1">
+    <row r="27" spans="1:81" ht="15.95" customHeight="1">
+      <c r="A27" s="32" t="str" cm="1">
         <f t="array" ref="A27">IF($CC27="","",INDEX(Tasks!A$4:A$43,$CC27))</f>
         <v/>
       </c>
-      <c r="B27" s="15" t="str" cm="1">
+      <c r="B27" s="33" t="str" cm="1">
         <f t="array" ref="B27">IF($CC27="","",INDEX(Tasks!B$4:B$43,$CC27))</f>
         <v/>
       </c>
-      <c r="C27" s="16" t="str" cm="1">
+      <c r="C27" s="34" t="str" cm="1">
         <f t="array" ref="C27">IF($CC27="","",INDEX(Tasks!C$4:C$43,$CC27))</f>
         <v/>
       </c>
-      <c r="D27" s="22" t="str" cm="1">
+      <c r="D27" s="35" t="str" cm="1">
         <f t="array" ref="D27">IF($CC27="","",INDEX(Tasks!D$4:D$43,$CC27))</f>
         <v/>
       </c>
-      <c r="E27" s="31" t="str" cm="1">
+      <c r="E27" s="36" t="str" cm="1">
         <f t="array" ref="E27">IF($CC27="","",INDEX(Tasks!E$4:E$43,$CC27))</f>
         <v/>
       </c>
-      <c r="F27" s="22" t="str" cm="1">
+      <c r="F27" s="35" t="str" cm="1">
         <f t="array" ref="F27">IF($CC27="","",INDEX(Tasks!F$4:F$43,$CC27))</f>
         <v/>
       </c>
-      <c r="G27" s="31" t="str" cm="1">
+      <c r="G27" s="36" t="str" cm="1">
         <f t="array" ref="G27">IF($CC27="","",INDEX(Tasks!G$4:G$43,$CC27))</f>
         <v/>
       </c>
-      <c r="H27" s="23" t="str" cm="1">
+      <c r="H27" s="37" t="str" cm="1">
         <f t="array" ref="H27">IF($CC27="","",INDEX(Tasks!H$4:H$43,$CC27))</f>
         <v/>
       </c>
@@ -9436,45 +9472,46 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="CB27" t="str" cm="1">
+      <c r="CA27" s="38"/>
+      <c r="CB27" s="38" t="str" cm="1">
         <f t="array" ref="CB27">IF(Tasks!C27="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E27)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E27)*(Tasks!$A$4:$A$43&lt;Tasks!A27)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v/>
       </c>
-      <c r="CC27" t="str">
+      <c r="CC27" s="38" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="14" t="str" cm="1">
+    <row r="28" spans="1:81" ht="15.95" customHeight="1">
+      <c r="A28" s="32" t="str" cm="1">
         <f t="array" ref="A28">IF($CC28="","",INDEX(Tasks!A$4:A$43,$CC28))</f>
         <v/>
       </c>
-      <c r="B28" s="15" t="str" cm="1">
+      <c r="B28" s="33" t="str" cm="1">
         <f t="array" ref="B28">IF($CC28="","",INDEX(Tasks!B$4:B$43,$CC28))</f>
         <v/>
       </c>
-      <c r="C28" s="16" t="str" cm="1">
+      <c r="C28" s="34" t="str" cm="1">
         <f t="array" ref="C28">IF($CC28="","",INDEX(Tasks!C$4:C$43,$CC28))</f>
         <v/>
       </c>
-      <c r="D28" s="22" t="str" cm="1">
+      <c r="D28" s="35" t="str" cm="1">
         <f t="array" ref="D28">IF($CC28="","",INDEX(Tasks!D$4:D$43,$CC28))</f>
         <v/>
       </c>
-      <c r="E28" s="31" t="str" cm="1">
+      <c r="E28" s="36" t="str" cm="1">
         <f t="array" ref="E28">IF($CC28="","",INDEX(Tasks!E$4:E$43,$CC28))</f>
         <v/>
       </c>
-      <c r="F28" s="22" t="str" cm="1">
+      <c r="F28" s="35" t="str" cm="1">
         <f t="array" ref="F28">IF($CC28="","",INDEX(Tasks!F$4:F$43,$CC28))</f>
         <v/>
       </c>
-      <c r="G28" s="31" t="str" cm="1">
+      <c r="G28" s="36" t="str" cm="1">
         <f t="array" ref="G28">IF($CC28="","",INDEX(Tasks!G$4:G$43,$CC28))</f>
         <v/>
       </c>
-      <c r="H28" s="23" t="str" cm="1">
+      <c r="H28" s="37" t="str" cm="1">
         <f t="array" ref="H28">IF($CC28="","",INDEX(Tasks!H$4:H$43,$CC28))</f>
         <v/>
       </c>
@@ -9758,45 +9795,46 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="CB28" t="str" cm="1">
+      <c r="CA28" s="38"/>
+      <c r="CB28" s="38" t="str" cm="1">
         <f t="array" ref="CB28">IF(Tasks!C28="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E28)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E28)*(Tasks!$A$4:$A$43&lt;Tasks!A28)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v/>
       </c>
-      <c r="CC28" t="str">
+      <c r="CC28" s="38" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="14" t="str" cm="1">
+    <row r="29" spans="1:81" ht="15.95" customHeight="1">
+      <c r="A29" s="32" t="str" cm="1">
         <f t="array" ref="A29">IF($CC29="","",INDEX(Tasks!A$4:A$43,$CC29))</f>
         <v/>
       </c>
-      <c r="B29" s="15" t="str" cm="1">
+      <c r="B29" s="33" t="str" cm="1">
         <f t="array" ref="B29">IF($CC29="","",INDEX(Tasks!B$4:B$43,$CC29))</f>
         <v/>
       </c>
-      <c r="C29" s="16" t="str" cm="1">
+      <c r="C29" s="34" t="str" cm="1">
         <f t="array" ref="C29">IF($CC29="","",INDEX(Tasks!C$4:C$43,$CC29))</f>
         <v/>
       </c>
-      <c r="D29" s="22" t="str" cm="1">
+      <c r="D29" s="35" t="str" cm="1">
         <f t="array" ref="D29">IF($CC29="","",INDEX(Tasks!D$4:D$43,$CC29))</f>
         <v/>
       </c>
-      <c r="E29" s="31" t="str" cm="1">
+      <c r="E29" s="36" t="str" cm="1">
         <f t="array" ref="E29">IF($CC29="","",INDEX(Tasks!E$4:E$43,$CC29))</f>
         <v/>
       </c>
-      <c r="F29" s="22" t="str" cm="1">
+      <c r="F29" s="35" t="str" cm="1">
         <f t="array" ref="F29">IF($CC29="","",INDEX(Tasks!F$4:F$43,$CC29))</f>
         <v/>
       </c>
-      <c r="G29" s="31" t="str" cm="1">
+      <c r="G29" s="36" t="str" cm="1">
         <f t="array" ref="G29">IF($CC29="","",INDEX(Tasks!G$4:G$43,$CC29))</f>
         <v/>
       </c>
-      <c r="H29" s="23" t="str" cm="1">
+      <c r="H29" s="37" t="str" cm="1">
         <f t="array" ref="H29">IF($CC29="","",INDEX(Tasks!H$4:H$43,$CC29))</f>
         <v/>
       </c>
@@ -10080,45 +10118,46 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="CB29" t="str" cm="1">
+      <c r="CA29" s="38"/>
+      <c r="CB29" s="38" t="str" cm="1">
         <f t="array" ref="CB29">IF(Tasks!C29="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E29)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E29)*(Tasks!$A$4:$A$43&lt;Tasks!A29)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v/>
       </c>
-      <c r="CC29" t="str">
+      <c r="CC29" s="38" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="14" t="str" cm="1">
+    <row r="30" spans="1:81" ht="15.95" customHeight="1">
+      <c r="A30" s="32" t="str" cm="1">
         <f t="array" ref="A30">IF($CC30="","",INDEX(Tasks!A$4:A$43,$CC30))</f>
         <v/>
       </c>
-      <c r="B30" s="15" t="str" cm="1">
+      <c r="B30" s="33" t="str" cm="1">
         <f t="array" ref="B30">IF($CC30="","",INDEX(Tasks!B$4:B$43,$CC30))</f>
         <v/>
       </c>
-      <c r="C30" s="16" t="str" cm="1">
+      <c r="C30" s="34" t="str" cm="1">
         <f t="array" ref="C30">IF($CC30="","",INDEX(Tasks!C$4:C$43,$CC30))</f>
         <v/>
       </c>
-      <c r="D30" s="22" t="str" cm="1">
+      <c r="D30" s="35" t="str" cm="1">
         <f t="array" ref="D30">IF($CC30="","",INDEX(Tasks!D$4:D$43,$CC30))</f>
         <v/>
       </c>
-      <c r="E30" s="31" t="str" cm="1">
+      <c r="E30" s="36" t="str" cm="1">
         <f t="array" ref="E30">IF($CC30="","",INDEX(Tasks!E$4:E$43,$CC30))</f>
         <v/>
       </c>
-      <c r="F30" s="22" t="str" cm="1">
+      <c r="F30" s="35" t="str" cm="1">
         <f t="array" ref="F30">IF($CC30="","",INDEX(Tasks!F$4:F$43,$CC30))</f>
         <v/>
       </c>
-      <c r="G30" s="31" t="str" cm="1">
+      <c r="G30" s="36" t="str" cm="1">
         <f t="array" ref="G30">IF($CC30="","",INDEX(Tasks!G$4:G$43,$CC30))</f>
         <v/>
       </c>
-      <c r="H30" s="23" t="str" cm="1">
+      <c r="H30" s="37" t="str" cm="1">
         <f t="array" ref="H30">IF($CC30="","",INDEX(Tasks!H$4:H$43,$CC30))</f>
         <v/>
       </c>
@@ -10402,45 +10441,46 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="CB30" t="str" cm="1">
+      <c r="CA30" s="38"/>
+      <c r="CB30" s="38" t="str" cm="1">
         <f t="array" ref="CB30">IF(Tasks!C30="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E30)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E30)*(Tasks!$A$4:$A$43&lt;Tasks!A30)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v/>
       </c>
-      <c r="CC30" t="str">
+      <c r="CC30" s="38" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="14" t="str" cm="1">
+    <row r="31" spans="1:81" ht="15.95" customHeight="1">
+      <c r="A31" s="32" t="str" cm="1">
         <f t="array" ref="A31">IF($CC31="","",INDEX(Tasks!A$4:A$43,$CC31))</f>
         <v/>
       </c>
-      <c r="B31" s="15" t="str" cm="1">
+      <c r="B31" s="33" t="str" cm="1">
         <f t="array" ref="B31">IF($CC31="","",INDEX(Tasks!B$4:B$43,$CC31))</f>
         <v/>
       </c>
-      <c r="C31" s="16" t="str" cm="1">
+      <c r="C31" s="34" t="str" cm="1">
         <f t="array" ref="C31">IF($CC31="","",INDEX(Tasks!C$4:C$43,$CC31))</f>
         <v/>
       </c>
-      <c r="D31" s="22" t="str" cm="1">
+      <c r="D31" s="35" t="str" cm="1">
         <f t="array" ref="D31">IF($CC31="","",INDEX(Tasks!D$4:D$43,$CC31))</f>
         <v/>
       </c>
-      <c r="E31" s="31" t="str" cm="1">
+      <c r="E31" s="36" t="str" cm="1">
         <f t="array" ref="E31">IF($CC31="","",INDEX(Tasks!E$4:E$43,$CC31))</f>
         <v/>
       </c>
-      <c r="F31" s="22" t="str" cm="1">
+      <c r="F31" s="35" t="str" cm="1">
         <f t="array" ref="F31">IF($CC31="","",INDEX(Tasks!F$4:F$43,$CC31))</f>
         <v/>
       </c>
-      <c r="G31" s="31" t="str" cm="1">
+      <c r="G31" s="36" t="str" cm="1">
         <f t="array" ref="G31">IF($CC31="","",INDEX(Tasks!G$4:G$43,$CC31))</f>
         <v/>
       </c>
-      <c r="H31" s="23" t="str" cm="1">
+      <c r="H31" s="37" t="str" cm="1">
         <f t="array" ref="H31">IF($CC31="","",INDEX(Tasks!H$4:H$43,$CC31))</f>
         <v/>
       </c>
@@ -10724,45 +10764,46 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="CB31" t="str" cm="1">
+      <c r="CA31" s="38"/>
+      <c r="CB31" s="38" t="str" cm="1">
         <f t="array" ref="CB31">IF(Tasks!C31="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E31)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E31)*(Tasks!$A$4:$A$43&lt;Tasks!A31)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v/>
       </c>
-      <c r="CC31" t="str">
+      <c r="CC31" s="38" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="14" t="str" cm="1">
+    <row r="32" spans="1:81" ht="15.95" customHeight="1">
+      <c r="A32" s="32" t="str" cm="1">
         <f t="array" ref="A32">IF($CC32="","",INDEX(Tasks!A$4:A$43,$CC32))</f>
         <v/>
       </c>
-      <c r="B32" s="15" t="str" cm="1">
+      <c r="B32" s="33" t="str" cm="1">
         <f t="array" ref="B32">IF($CC32="","",INDEX(Tasks!B$4:B$43,$CC32))</f>
         <v/>
       </c>
-      <c r="C32" s="16" t="str" cm="1">
+      <c r="C32" s="34" t="str" cm="1">
         <f t="array" ref="C32">IF($CC32="","",INDEX(Tasks!C$4:C$43,$CC32))</f>
         <v/>
       </c>
-      <c r="D32" s="22" t="str" cm="1">
+      <c r="D32" s="35" t="str" cm="1">
         <f t="array" ref="D32">IF($CC32="","",INDEX(Tasks!D$4:D$43,$CC32))</f>
         <v/>
       </c>
-      <c r="E32" s="31" t="str" cm="1">
+      <c r="E32" s="36" t="str" cm="1">
         <f t="array" ref="E32">IF($CC32="","",INDEX(Tasks!E$4:E$43,$CC32))</f>
         <v/>
       </c>
-      <c r="F32" s="22" t="str" cm="1">
+      <c r="F32" s="35" t="str" cm="1">
         <f t="array" ref="F32">IF($CC32="","",INDEX(Tasks!F$4:F$43,$CC32))</f>
         <v/>
       </c>
-      <c r="G32" s="31" t="str" cm="1">
+      <c r="G32" s="36" t="str" cm="1">
         <f t="array" ref="G32">IF($CC32="","",INDEX(Tasks!G$4:G$43,$CC32))</f>
         <v/>
       </c>
-      <c r="H32" s="23" t="str" cm="1">
+      <c r="H32" s="37" t="str" cm="1">
         <f t="array" ref="H32">IF($CC32="","",INDEX(Tasks!H$4:H$43,$CC32))</f>
         <v/>
       </c>
@@ -11046,45 +11087,46 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="CB32" t="str" cm="1">
+      <c r="CA32" s="38"/>
+      <c r="CB32" s="38" t="str" cm="1">
         <f t="array" ref="CB32">IF(Tasks!C32="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E32)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E32)*(Tasks!$A$4:$A$43&lt;Tasks!A32)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v/>
       </c>
-      <c r="CC32" t="str">
+      <c r="CC32" s="38" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="14" t="str" cm="1">
+    <row r="33" spans="1:81" ht="15.95" customHeight="1">
+      <c r="A33" s="32" t="str" cm="1">
         <f t="array" ref="A33">IF($CC33="","",INDEX(Tasks!A$4:A$43,$CC33))</f>
         <v/>
       </c>
-      <c r="B33" s="15" t="str" cm="1">
+      <c r="B33" s="33" t="str" cm="1">
         <f t="array" ref="B33">IF($CC33="","",INDEX(Tasks!B$4:B$43,$CC33))</f>
         <v/>
       </c>
-      <c r="C33" s="16" t="str" cm="1">
+      <c r="C33" s="34" t="str" cm="1">
         <f t="array" ref="C33">IF($CC33="","",INDEX(Tasks!C$4:C$43,$CC33))</f>
         <v/>
       </c>
-      <c r="D33" s="22" t="str" cm="1">
+      <c r="D33" s="35" t="str" cm="1">
         <f t="array" ref="D33">IF($CC33="","",INDEX(Tasks!D$4:D$43,$CC33))</f>
         <v/>
       </c>
-      <c r="E33" s="31" t="str" cm="1">
+      <c r="E33" s="36" t="str" cm="1">
         <f t="array" ref="E33">IF($CC33="","",INDEX(Tasks!E$4:E$43,$CC33))</f>
         <v/>
       </c>
-      <c r="F33" s="22" t="str" cm="1">
+      <c r="F33" s="35" t="str" cm="1">
         <f t="array" ref="F33">IF($CC33="","",INDEX(Tasks!F$4:F$43,$CC33))</f>
         <v/>
       </c>
-      <c r="G33" s="31" t="str" cm="1">
+      <c r="G33" s="36" t="str" cm="1">
         <f t="array" ref="G33">IF($CC33="","",INDEX(Tasks!G$4:G$43,$CC33))</f>
         <v/>
       </c>
-      <c r="H33" s="23" t="str" cm="1">
+      <c r="H33" s="37" t="str" cm="1">
         <f t="array" ref="H33">IF($CC33="","",INDEX(Tasks!H$4:H$43,$CC33))</f>
         <v/>
       </c>
@@ -11368,282 +11410,764 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="CB33" t="str" cm="1">
+      <c r="CA33" s="38"/>
+      <c r="CB33" s="38" t="str" cm="1">
         <f t="array" ref="CB33">IF(Tasks!C33="","",SUMPRODUCT((Tasks!$E$4:$E$43&lt;Tasks!E33)*(Tasks!$C$4:$C$43&lt;&gt;""))+SUMPRODUCT((Tasks!$E$4:$E$43=Tasks!E33)*(Tasks!$A$4:$A$43&lt;Tasks!A33)*(Tasks!$C$4:$C$43&lt;&gt;""))+1)</f>
         <v/>
       </c>
-      <c r="CC33" t="str">
+      <c r="CC33" s="38" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="14" t="str" cm="1">
+    <row r="34" spans="1:81" ht="15.95" customHeight="1">
+      <c r="A34" s="32" t="str" cm="1">
         <f t="array" ref="A34">IF($CC34="","",INDEX(Tasks!A$4:A$43,$CC34))</f>
         <v/>
       </c>
-      <c r="B34" s="15" t="str" cm="1">
+      <c r="B34" s="33" t="str" cm="1">
         <f t="array" ref="B34">IF($CC34="","",INDEX(Tasks!B$4:B$43,$CC34))</f>
         <v/>
       </c>
-      <c r="C34" s="16" t="str" cm="1">
+      <c r="C34" s="34" t="str" cm="1">
         <f t="array" ref="C34">IF($CC34="","",INDEX(Tasks!C$4:C$43,$CC34))</f>
         <v/>
       </c>
-      <c r="D34" s="22" t="str" cm="1">
+      <c r="D34" s="35" t="str" cm="1">
         <f t="array" ref="D34">IF($CC34="","",INDEX(Tasks!D$4:D$43,$CC34))</f>
         <v/>
       </c>
-      <c r="E34" s="31" t="str" cm="1">
+      <c r="E34" s="36" t="str" cm="1">
         <f t="array" ref="E34">IF($CC34="","",INDEX(Tasks!E$4:E$43,$CC34))</f>
         <v/>
       </c>
-      <c r="F34" s="22" t="str" cm="1">
+      <c r="F34" s="35" t="str" cm="1">
         <f t="array" ref="F34">IF($CC34="","",INDEX(Tasks!F$4:F$43,$CC34))</f>
         <v/>
       </c>
-      <c r="G34" s="31" t="str" cm="1">
+      <c r="G34" s="36" t="str" cm="1">
         <f t="array" ref="G34">IF($CC34="","",INDEX(Tasks!G$4:G$43,$CC34))</f>
         <v/>
       </c>
-      <c r="H34" s="23" t="str" cm="1">
+      <c r="H34" s="37" t="str" cm="1">
         <f t="array" ref="H34">IF($CC34="","",INDEX(Tasks!H$4:H$43,$CC34))</f>
         <v/>
       </c>
+      <c r="I34" s="38"/>
+      <c r="J34" s="38"/>
+      <c r="K34" s="38"/>
+      <c r="L34" s="38"/>
+      <c r="M34" s="38"/>
+      <c r="N34" s="38"/>
+      <c r="O34" s="38"/>
+      <c r="P34" s="38"/>
+      <c r="Q34" s="38"/>
+      <c r="R34" s="38"/>
+      <c r="S34" s="38"/>
+      <c r="T34" s="38"/>
+      <c r="U34" s="38"/>
+      <c r="V34" s="38"/>
+      <c r="W34" s="38"/>
+      <c r="X34" s="38"/>
+      <c r="Y34" s="38"/>
+      <c r="Z34" s="38"/>
+      <c r="AA34" s="38"/>
+      <c r="AB34" s="38"/>
+      <c r="AC34" s="38"/>
+      <c r="AD34" s="38"/>
+      <c r="AE34" s="38"/>
+      <c r="AF34" s="38"/>
+      <c r="AG34" s="38"/>
+      <c r="AH34" s="38"/>
+      <c r="AI34" s="38"/>
+      <c r="AJ34" s="38"/>
+      <c r="AK34" s="38"/>
+      <c r="AL34" s="38"/>
+      <c r="AM34" s="38"/>
+      <c r="AN34" s="38"/>
+      <c r="AO34" s="38"/>
+      <c r="AP34" s="38"/>
+      <c r="AQ34" s="38"/>
+      <c r="AR34" s="38"/>
+      <c r="AS34" s="38"/>
+      <c r="AT34" s="38"/>
+      <c r="AU34" s="38"/>
+      <c r="AV34" s="38"/>
+      <c r="AW34" s="38"/>
+      <c r="AX34" s="38"/>
+      <c r="AY34" s="38"/>
+      <c r="AZ34" s="38"/>
+      <c r="BA34" s="38"/>
+      <c r="BB34" s="38"/>
+      <c r="BC34" s="38"/>
+      <c r="BD34" s="38"/>
+      <c r="BE34" s="38"/>
+      <c r="BF34" s="38"/>
+      <c r="BG34" s="38"/>
+      <c r="BH34" s="38"/>
+      <c r="BI34" s="38"/>
+      <c r="BJ34" s="38"/>
+      <c r="BK34" s="38"/>
+      <c r="BL34" s="38"/>
+      <c r="BM34" s="38"/>
+      <c r="BN34" s="38"/>
+      <c r="BO34" s="38"/>
+      <c r="BP34" s="38"/>
+      <c r="BQ34" s="38"/>
+      <c r="BR34" s="38"/>
+      <c r="BS34" s="38"/>
+      <c r="BT34" s="38"/>
+      <c r="BU34" s="38"/>
+      <c r="BV34" s="38"/>
+      <c r="BW34" s="38"/>
+      <c r="BX34" s="38"/>
+      <c r="BY34" s="38"/>
+      <c r="BZ34" s="38"/>
+      <c r="CA34" s="38"/>
+      <c r="CB34" s="38"/>
+      <c r="CC34" s="38"/>
     </row>
-    <row r="35" spans="1:81" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="42" t="str" cm="1">
+    <row r="35" spans="1:81" ht="15.95" customHeight="1">
+      <c r="A35" s="43" t="str" cm="1">
         <f t="array" ref="A35">IF($CC35="","",INDEX(Tasks!A$4:A$43,$CC35))</f>
         <v/>
       </c>
-      <c r="B35" s="43" t="str" cm="1">
+      <c r="B35" s="44" t="str" cm="1">
         <f t="array" ref="B35">IF($CC35="","",INDEX(Tasks!B$4:B$43,$CC35))</f>
         <v/>
       </c>
-      <c r="C35" s="44" t="str" cm="1">
+      <c r="C35" s="45" t="str" cm="1">
         <f t="array" ref="C35">IF($CC35="","",INDEX(Tasks!C$4:C$43,$CC35))</f>
         <v/>
       </c>
-      <c r="D35" s="45" t="str" cm="1">
+      <c r="D35" s="46" t="str" cm="1">
         <f t="array" ref="D35">IF($CC35="","",INDEX(Tasks!D$4:D$43,$CC35))</f>
         <v/>
       </c>
-      <c r="E35" s="46" t="str" cm="1">
+      <c r="E35" s="47" t="str" cm="1">
         <f t="array" ref="E35">IF($CC35="","",INDEX(Tasks!E$4:E$43,$CC35))</f>
         <v/>
       </c>
-      <c r="F35" s="45" t="str" cm="1">
+      <c r="F35" s="46" t="str" cm="1">
         <f t="array" ref="F35">IF($CC35="","",INDEX(Tasks!F$4:F$43,$CC35))</f>
         <v/>
       </c>
-      <c r="G35" s="46" t="str" cm="1">
+      <c r="G35" s="47" t="str" cm="1">
         <f t="array" ref="G35">IF($CC35="","",INDEX(Tasks!G$4:G$43,$CC35))</f>
         <v/>
       </c>
-      <c r="H35" s="47" t="str" cm="1">
+      <c r="H35" s="48" t="str" cm="1">
         <f t="array" ref="H35">IF($CC35="","",INDEX(Tasks!H$4:H$43,$CC35))</f>
         <v/>
       </c>
-      <c r="I35" s="48"/>
-      <c r="J35" s="48"/>
-      <c r="K35" s="48"/>
-      <c r="L35" s="48"/>
-      <c r="M35" s="48"/>
-      <c r="N35" s="48"/>
-      <c r="P35" s="48"/>
-      <c r="Q35" s="48"/>
-      <c r="R35" s="48"/>
-      <c r="S35" s="48"/>
-      <c r="T35" s="48"/>
-      <c r="U35" s="48"/>
-      <c r="W35" s="48"/>
-      <c r="X35" s="48"/>
-      <c r="Y35" s="48"/>
-      <c r="Z35" s="48"/>
-      <c r="AA35" s="48"/>
-      <c r="AB35" s="48"/>
-      <c r="AD35" s="48"/>
-      <c r="AE35" s="48"/>
-      <c r="AF35" s="48"/>
-      <c r="AG35" s="48"/>
-      <c r="AH35" s="48"/>
-      <c r="AI35" s="48"/>
-      <c r="AK35" s="48"/>
-      <c r="AL35" s="48"/>
-      <c r="AM35" s="48"/>
-      <c r="AN35" s="48"/>
-      <c r="AO35" s="48"/>
-      <c r="AP35" s="48"/>
+      <c r="I35" s="55"/>
+      <c r="J35" s="55"/>
+      <c r="K35" s="55"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="55"/>
+      <c r="N35" s="55"/>
+      <c r="O35" s="38"/>
+      <c r="P35" s="55"/>
+      <c r="Q35" s="55"/>
+      <c r="R35" s="55"/>
+      <c r="S35" s="55"/>
+      <c r="T35" s="55"/>
+      <c r="U35" s="55"/>
+      <c r="V35" s="38"/>
+      <c r="W35" s="55"/>
+      <c r="X35" s="55"/>
+      <c r="Y35" s="55"/>
+      <c r="Z35" s="55"/>
+      <c r="AA35" s="55"/>
+      <c r="AB35" s="55"/>
+      <c r="AC35" s="38"/>
+      <c r="AD35" s="55"/>
+      <c r="AE35" s="55"/>
+      <c r="AF35" s="55"/>
+      <c r="AG35" s="55"/>
+      <c r="AH35" s="55"/>
+      <c r="AI35" s="55"/>
+      <c r="AJ35" s="38"/>
+      <c r="AK35" s="55"/>
+      <c r="AL35" s="55"/>
+      <c r="AM35" s="55"/>
+      <c r="AN35" s="55"/>
+      <c r="AO35" s="55"/>
+      <c r="AP35" s="55"/>
+      <c r="AQ35" s="38"/>
+      <c r="AR35" s="38"/>
+      <c r="AS35" s="38"/>
+      <c r="AT35" s="38"/>
+      <c r="AU35" s="38"/>
+      <c r="AV35" s="38"/>
+      <c r="AW35" s="38"/>
+      <c r="AX35" s="38"/>
+      <c r="AY35" s="38"/>
+      <c r="AZ35" s="38"/>
+      <c r="BA35" s="38"/>
+      <c r="BB35" s="38"/>
+      <c r="BC35" s="38"/>
+      <c r="BD35" s="38"/>
+      <c r="BE35" s="38"/>
+      <c r="BF35" s="38"/>
+      <c r="BG35" s="38"/>
+      <c r="BH35" s="38"/>
+      <c r="BI35" s="38"/>
+      <c r="BJ35" s="38"/>
+      <c r="BK35" s="38"/>
+      <c r="BL35" s="38"/>
+      <c r="BM35" s="38"/>
+      <c r="BN35" s="38"/>
+      <c r="BO35" s="38"/>
+      <c r="BP35" s="38"/>
+      <c r="BQ35" s="38"/>
+      <c r="BR35" s="38"/>
+      <c r="BS35" s="38"/>
+      <c r="BT35" s="38"/>
+      <c r="BU35" s="38"/>
+      <c r="BV35" s="38"/>
+      <c r="BW35" s="38"/>
+      <c r="BX35" s="38"/>
+      <c r="BY35" s="38"/>
+      <c r="BZ35" s="38"/>
+      <c r="CA35" s="38"/>
+      <c r="CB35" s="38"/>
+      <c r="CC35" s="38"/>
     </row>
-    <row r="36" spans="1:81" ht="15" x14ac:dyDescent="0.2">
-      <c r="A36" s="14" t="str" cm="1">
+    <row r="36" spans="1:81" ht="15">
+      <c r="A36" s="32" t="str" cm="1">
         <f t="array" ref="A36">IF($CC36="","",INDEX(Tasks!A$4:A$43,$CC36))</f>
         <v/>
       </c>
-      <c r="B36" s="15" t="str" cm="1">
+      <c r="B36" s="33" t="str" cm="1">
         <f t="array" ref="B36">IF($CC36="","",INDEX(Tasks!B$4:B$43,$CC36))</f>
         <v/>
       </c>
-      <c r="C36" s="16" t="str" cm="1">
+      <c r="C36" s="34" t="str" cm="1">
         <f t="array" ref="C36">IF($CC36="","",INDEX(Tasks!C$4:C$43,$CC36))</f>
         <v/>
       </c>
-      <c r="D36" s="22" t="str" cm="1">
+      <c r="D36" s="35" t="str" cm="1">
         <f t="array" ref="D36">IF($CC36="","",INDEX(Tasks!D$4:D$43,$CC36))</f>
         <v/>
       </c>
-      <c r="E36" s="31" t="str" cm="1">
+      <c r="E36" s="36" t="str" cm="1">
         <f t="array" ref="E36">IF($CC36="","",INDEX(Tasks!E$4:E$43,$CC36))</f>
         <v/>
       </c>
-      <c r="F36" s="22" t="str" cm="1">
+      <c r="F36" s="35" t="str" cm="1">
         <f t="array" ref="F36">IF($CC36="","",INDEX(Tasks!F$4:F$43,$CC36))</f>
         <v/>
       </c>
-      <c r="G36" s="31" t="str" cm="1">
+      <c r="G36" s="36" t="str" cm="1">
         <f t="array" ref="G36">IF($CC36="","",INDEX(Tasks!G$4:G$43,$CC36))</f>
         <v/>
       </c>
-      <c r="H36" s="23" t="str" cm="1">
+      <c r="H36" s="37" t="str" cm="1">
         <f t="array" ref="H36">IF($CC36="","",INDEX(Tasks!H$4:H$43,$CC36))</f>
         <v/>
       </c>
+      <c r="I36" s="38"/>
+      <c r="J36" s="38"/>
+      <c r="K36" s="38"/>
+      <c r="L36" s="38"/>
+      <c r="M36" s="38"/>
+      <c r="N36" s="38"/>
+      <c r="O36" s="38"/>
+      <c r="P36" s="38"/>
+      <c r="Q36" s="38"/>
+      <c r="R36" s="38"/>
+      <c r="S36" s="38"/>
+      <c r="T36" s="38"/>
+      <c r="U36" s="38"/>
+      <c r="V36" s="38"/>
+      <c r="W36" s="38"/>
+      <c r="X36" s="38"/>
+      <c r="Y36" s="38"/>
+      <c r="Z36" s="38"/>
+      <c r="AA36" s="38"/>
+      <c r="AB36" s="38"/>
+      <c r="AC36" s="38"/>
+      <c r="AD36" s="38"/>
+      <c r="AE36" s="38"/>
+      <c r="AF36" s="38"/>
+      <c r="AG36" s="38"/>
+      <c r="AH36" s="38"/>
+      <c r="AI36" s="38"/>
+      <c r="AJ36" s="38"/>
+      <c r="AK36" s="38"/>
+      <c r="AL36" s="38"/>
+      <c r="AM36" s="38"/>
+      <c r="AN36" s="38"/>
+      <c r="AO36" s="38"/>
+      <c r="AP36" s="38"/>
+      <c r="AQ36" s="38"/>
+      <c r="AR36" s="38"/>
+      <c r="AS36" s="38"/>
+      <c r="AT36" s="38"/>
+      <c r="AU36" s="38"/>
+      <c r="AV36" s="38"/>
+      <c r="AW36" s="38"/>
+      <c r="AX36" s="38"/>
+      <c r="AY36" s="38"/>
+      <c r="AZ36" s="38"/>
+      <c r="BA36" s="38"/>
+      <c r="BB36" s="38"/>
+      <c r="BC36" s="38"/>
+      <c r="BD36" s="38"/>
+      <c r="BE36" s="38"/>
+      <c r="BF36" s="38"/>
+      <c r="BG36" s="38"/>
+      <c r="BH36" s="38"/>
+      <c r="BI36" s="38"/>
+      <c r="BJ36" s="38"/>
+      <c r="BK36" s="38"/>
+      <c r="BL36" s="38"/>
+      <c r="BM36" s="38"/>
+      <c r="BN36" s="38"/>
+      <c r="BO36" s="38"/>
+      <c r="BP36" s="38"/>
+      <c r="BQ36" s="38"/>
+      <c r="BR36" s="38"/>
+      <c r="BS36" s="38"/>
+      <c r="BT36" s="38"/>
+      <c r="BU36" s="38"/>
+      <c r="BV36" s="38"/>
+      <c r="BW36" s="38"/>
+      <c r="BX36" s="38"/>
+      <c r="BY36" s="38"/>
+      <c r="BZ36" s="38"/>
+      <c r="CA36" s="38"/>
+      <c r="CB36" s="38"/>
+      <c r="CC36" s="38"/>
     </row>
-    <row r="37" spans="1:81" ht="15" x14ac:dyDescent="0.2">
-      <c r="A37" s="14" t="str" cm="1">
+    <row r="37" spans="1:81" ht="15">
+      <c r="A37" s="32" t="str" cm="1">
         <f t="array" ref="A37">IF($CC37="","",INDEX(Tasks!A$4:A$43,$CC37))</f>
         <v/>
       </c>
-      <c r="B37" s="15" t="str" cm="1">
+      <c r="B37" s="33" t="str" cm="1">
         <f t="array" ref="B37">IF($CC37="","",INDEX(Tasks!B$4:B$43,$CC37))</f>
         <v/>
       </c>
-      <c r="C37" s="16" t="str" cm="1">
+      <c r="C37" s="34" t="str" cm="1">
         <f t="array" ref="C37">IF($CC37="","",INDEX(Tasks!C$4:C$43,$CC37))</f>
         <v/>
       </c>
-      <c r="D37" s="22" t="str" cm="1">
+      <c r="D37" s="35" t="str" cm="1">
         <f t="array" ref="D37">IF($CC37="","",INDEX(Tasks!D$4:D$43,$CC37))</f>
         <v/>
       </c>
-      <c r="E37" s="31" t="str" cm="1">
+      <c r="E37" s="36" t="str" cm="1">
         <f t="array" ref="E37">IF($CC37="","",INDEX(Tasks!E$4:E$43,$CC37))</f>
         <v/>
       </c>
-      <c r="F37" s="22" t="str" cm="1">
+      <c r="F37" s="35" t="str" cm="1">
         <f t="array" ref="F37">IF($CC37="","",INDEX(Tasks!F$4:F$43,$CC37))</f>
         <v/>
       </c>
-      <c r="G37" s="31" t="str" cm="1">
+      <c r="G37" s="36" t="str" cm="1">
         <f t="array" ref="G37">IF($CC37="","",INDEX(Tasks!G$4:G$43,$CC37))</f>
         <v/>
       </c>
-      <c r="H37" s="23" t="str" cm="1">
+      <c r="H37" s="37" t="str" cm="1">
         <f t="array" ref="H37">IF($CC37="","",INDEX(Tasks!H$4:H$43,$CC37))</f>
         <v/>
       </c>
+      <c r="I37" s="38"/>
+      <c r="J37" s="38"/>
+      <c r="K37" s="38"/>
+      <c r="L37" s="38"/>
+      <c r="M37" s="38"/>
+      <c r="N37" s="38"/>
+      <c r="O37" s="38"/>
+      <c r="P37" s="38"/>
+      <c r="Q37" s="38"/>
+      <c r="R37" s="38"/>
+      <c r="S37" s="38"/>
+      <c r="T37" s="38"/>
+      <c r="U37" s="38"/>
+      <c r="V37" s="38"/>
+      <c r="W37" s="38"/>
+      <c r="X37" s="38"/>
+      <c r="Y37" s="38"/>
+      <c r="Z37" s="38"/>
+      <c r="AA37" s="38"/>
+      <c r="AB37" s="38"/>
+      <c r="AC37" s="38"/>
+      <c r="AD37" s="38"/>
+      <c r="AE37" s="38"/>
+      <c r="AF37" s="38"/>
+      <c r="AG37" s="38"/>
+      <c r="AH37" s="38"/>
+      <c r="AI37" s="38"/>
+      <c r="AJ37" s="38"/>
+      <c r="AK37" s="38"/>
+      <c r="AL37" s="38"/>
+      <c r="AM37" s="38"/>
+      <c r="AN37" s="38"/>
+      <c r="AO37" s="38"/>
+      <c r="AP37" s="38"/>
+      <c r="AQ37" s="38"/>
+      <c r="AR37" s="38"/>
+      <c r="AS37" s="38"/>
+      <c r="AT37" s="38"/>
+      <c r="AU37" s="38"/>
+      <c r="AV37" s="38"/>
+      <c r="AW37" s="38"/>
+      <c r="AX37" s="38"/>
+      <c r="AY37" s="38"/>
+      <c r="AZ37" s="38"/>
+      <c r="BA37" s="38"/>
+      <c r="BB37" s="38"/>
+      <c r="BC37" s="38"/>
+      <c r="BD37" s="38"/>
+      <c r="BE37" s="38"/>
+      <c r="BF37" s="38"/>
+      <c r="BG37" s="38"/>
+      <c r="BH37" s="38"/>
+      <c r="BI37" s="38"/>
+      <c r="BJ37" s="38"/>
+      <c r="BK37" s="38"/>
+      <c r="BL37" s="38"/>
+      <c r="BM37" s="38"/>
+      <c r="BN37" s="38"/>
+      <c r="BO37" s="38"/>
+      <c r="BP37" s="38"/>
+      <c r="BQ37" s="38"/>
+      <c r="BR37" s="38"/>
+      <c r="BS37" s="38"/>
+      <c r="BT37" s="38"/>
+      <c r="BU37" s="38"/>
+      <c r="BV37" s="38"/>
+      <c r="BW37" s="38"/>
+      <c r="BX37" s="38"/>
+      <c r="BY37" s="38"/>
+      <c r="BZ37" s="38"/>
+      <c r="CA37" s="38"/>
+      <c r="CB37" s="38"/>
+      <c r="CC37" s="38"/>
     </row>
-    <row r="38" spans="1:81" ht="15" x14ac:dyDescent="0.2">
-      <c r="A38" s="14" t="str" cm="1">
+    <row r="38" spans="1:81" ht="15">
+      <c r="A38" s="32" t="str" cm="1">
         <f t="array" ref="A38">IF($CC38="","",INDEX(Tasks!A$4:A$43,$CC38))</f>
         <v/>
       </c>
-      <c r="B38" s="15" t="str" cm="1">
+      <c r="B38" s="33" t="str" cm="1">
         <f t="array" ref="B38">IF($CC38="","",INDEX(Tasks!B$4:B$43,$CC38))</f>
         <v/>
       </c>
-      <c r="C38" s="16" t="str" cm="1">
+      <c r="C38" s="34" t="str" cm="1">
         <f t="array" ref="C38">IF($CC38="","",INDEX(Tasks!C$4:C$43,$CC38))</f>
         <v/>
       </c>
-      <c r="D38" s="22" t="str" cm="1">
+      <c r="D38" s="35" t="str" cm="1">
         <f t="array" ref="D38">IF($CC38="","",INDEX(Tasks!D$4:D$43,$CC38))</f>
         <v/>
       </c>
-      <c r="E38" s="31" t="str" cm="1">
+      <c r="E38" s="36" t="str" cm="1">
         <f t="array" ref="E38">IF($CC38="","",INDEX(Tasks!E$4:E$43,$CC38))</f>
         <v/>
       </c>
-      <c r="F38" s="22" t="str" cm="1">
+      <c r="F38" s="35" t="str" cm="1">
         <f t="array" ref="F38">IF($CC38="","",INDEX(Tasks!F$4:F$43,$CC38))</f>
         <v/>
       </c>
-      <c r="G38" s="31" t="str" cm="1">
+      <c r="G38" s="36" t="str" cm="1">
         <f t="array" ref="G38">IF($CC38="","",INDEX(Tasks!G$4:G$43,$CC38))</f>
         <v/>
       </c>
-      <c r="H38" s="23" t="str" cm="1">
+      <c r="H38" s="37" t="str" cm="1">
         <f t="array" ref="H38">IF($CC38="","",INDEX(Tasks!H$4:H$43,$CC38))</f>
         <v/>
       </c>
+      <c r="I38" s="38"/>
+      <c r="J38" s="38"/>
+      <c r="K38" s="38"/>
+      <c r="L38" s="38"/>
+      <c r="M38" s="38"/>
+      <c r="N38" s="38"/>
+      <c r="O38" s="38"/>
+      <c r="P38" s="38"/>
+      <c r="Q38" s="38"/>
+      <c r="R38" s="38"/>
+      <c r="S38" s="38"/>
+      <c r="T38" s="38"/>
+      <c r="U38" s="38"/>
+      <c r="V38" s="38"/>
+      <c r="W38" s="38"/>
+      <c r="X38" s="38"/>
+      <c r="Y38" s="38"/>
+      <c r="Z38" s="38"/>
+      <c r="AA38" s="38"/>
+      <c r="AB38" s="38"/>
+      <c r="AC38" s="38"/>
+      <c r="AD38" s="38"/>
+      <c r="AE38" s="38"/>
+      <c r="AF38" s="38"/>
+      <c r="AG38" s="38"/>
+      <c r="AH38" s="38"/>
+      <c r="AI38" s="38"/>
+      <c r="AJ38" s="38"/>
+      <c r="AK38" s="38"/>
+      <c r="AL38" s="38"/>
+      <c r="AM38" s="38"/>
+      <c r="AN38" s="38"/>
+      <c r="AO38" s="38"/>
+      <c r="AP38" s="38"/>
+      <c r="AQ38" s="38"/>
+      <c r="AR38" s="38"/>
+      <c r="AS38" s="38"/>
+      <c r="AT38" s="38"/>
+      <c r="AU38" s="38"/>
+      <c r="AV38" s="38"/>
+      <c r="AW38" s="38"/>
+      <c r="AX38" s="38"/>
+      <c r="AY38" s="38"/>
+      <c r="AZ38" s="38"/>
+      <c r="BA38" s="38"/>
+      <c r="BB38" s="38"/>
+      <c r="BC38" s="38"/>
+      <c r="BD38" s="38"/>
+      <c r="BE38" s="38"/>
+      <c r="BF38" s="38"/>
+      <c r="BG38" s="38"/>
+      <c r="BH38" s="38"/>
+      <c r="BI38" s="38"/>
+      <c r="BJ38" s="38"/>
+      <c r="BK38" s="38"/>
+      <c r="BL38" s="38"/>
+      <c r="BM38" s="38"/>
+      <c r="BN38" s="38"/>
+      <c r="BO38" s="38"/>
+      <c r="BP38" s="38"/>
+      <c r="BQ38" s="38"/>
+      <c r="BR38" s="38"/>
+      <c r="BS38" s="38"/>
+      <c r="BT38" s="38"/>
+      <c r="BU38" s="38"/>
+      <c r="BV38" s="38"/>
+      <c r="BW38" s="38"/>
+      <c r="BX38" s="38"/>
+      <c r="BY38" s="38"/>
+      <c r="BZ38" s="38"/>
+      <c r="CA38" s="38"/>
+      <c r="CB38" s="38"/>
+      <c r="CC38" s="38"/>
     </row>
-    <row r="39" spans="1:81" ht="15" x14ac:dyDescent="0.2">
-      <c r="A39" s="14" t="str" cm="1">
+    <row r="39" spans="1:81" ht="15">
+      <c r="A39" s="32" t="str" cm="1">
         <f t="array" ref="A39">IF($CC39="","",INDEX(Tasks!A$4:A$43,$CC39))</f>
         <v/>
       </c>
-      <c r="B39" s="15" t="str" cm="1">
+      <c r="B39" s="33" t="str" cm="1">
         <f t="array" ref="B39">IF($CC39="","",INDEX(Tasks!B$4:B$43,$CC39))</f>
         <v/>
       </c>
-      <c r="C39" s="16" t="str" cm="1">
+      <c r="C39" s="34" t="str" cm="1">
         <f t="array" ref="C39">IF($CC39="","",INDEX(Tasks!C$4:C$43,$CC39))</f>
         <v/>
       </c>
-      <c r="D39" s="22" t="str" cm="1">
+      <c r="D39" s="35" t="str" cm="1">
         <f t="array" ref="D39">IF($CC39="","",INDEX(Tasks!D$4:D$43,$CC39))</f>
         <v/>
       </c>
-      <c r="E39" s="31" t="str" cm="1">
+      <c r="E39" s="36" t="str" cm="1">
         <f t="array" ref="E39">IF($CC39="","",INDEX(Tasks!E$4:E$43,$CC39))</f>
         <v/>
       </c>
-      <c r="F39" s="22" t="str" cm="1">
+      <c r="F39" s="35" t="str" cm="1">
         <f t="array" ref="F39">IF($CC39="","",INDEX(Tasks!F$4:F$43,$CC39))</f>
         <v/>
       </c>
-      <c r="G39" s="31" t="str" cm="1">
+      <c r="G39" s="36" t="str" cm="1">
         <f t="array" ref="G39">IF($CC39="","",INDEX(Tasks!G$4:G$43,$CC39))</f>
         <v/>
       </c>
-      <c r="H39" s="23" t="str" cm="1">
+      <c r="H39" s="37" t="str" cm="1">
         <f t="array" ref="H39">IF($CC39="","",INDEX(Tasks!H$4:H$43,$CC39))</f>
         <v/>
       </c>
+      <c r="I39" s="38"/>
+      <c r="J39" s="38"/>
+      <c r="K39" s="38"/>
+      <c r="L39" s="38"/>
+      <c r="M39" s="38"/>
+      <c r="N39" s="38"/>
+      <c r="O39" s="38"/>
+      <c r="P39" s="38"/>
+      <c r="Q39" s="38"/>
+      <c r="R39" s="38"/>
+      <c r="S39" s="38"/>
+      <c r="T39" s="38"/>
+      <c r="U39" s="38"/>
+      <c r="V39" s="38"/>
+      <c r="W39" s="38"/>
+      <c r="X39" s="38"/>
+      <c r="Y39" s="38"/>
+      <c r="Z39" s="38"/>
+      <c r="AA39" s="38"/>
+      <c r="AB39" s="38"/>
+      <c r="AC39" s="38"/>
+      <c r="AD39" s="38"/>
+      <c r="AE39" s="38"/>
+      <c r="AF39" s="38"/>
+      <c r="AG39" s="38"/>
+      <c r="AH39" s="38"/>
+      <c r="AI39" s="38"/>
+      <c r="AJ39" s="38"/>
+      <c r="AK39" s="38"/>
+      <c r="AL39" s="38"/>
+      <c r="AM39" s="38"/>
+      <c r="AN39" s="38"/>
+      <c r="AO39" s="38"/>
+      <c r="AP39" s="38"/>
+      <c r="AQ39" s="38"/>
+      <c r="AR39" s="38"/>
+      <c r="AS39" s="38"/>
+      <c r="AT39" s="38"/>
+      <c r="AU39" s="38"/>
+      <c r="AV39" s="38"/>
+      <c r="AW39" s="38"/>
+      <c r="AX39" s="38"/>
+      <c r="AY39" s="38"/>
+      <c r="AZ39" s="38"/>
+      <c r="BA39" s="38"/>
+      <c r="BB39" s="38"/>
+      <c r="BC39" s="38"/>
+      <c r="BD39" s="38"/>
+      <c r="BE39" s="38"/>
+      <c r="BF39" s="38"/>
+      <c r="BG39" s="38"/>
+      <c r="BH39" s="38"/>
+      <c r="BI39" s="38"/>
+      <c r="BJ39" s="38"/>
+      <c r="BK39" s="38"/>
+      <c r="BL39" s="38"/>
+      <c r="BM39" s="38"/>
+      <c r="BN39" s="38"/>
+      <c r="BO39" s="38"/>
+      <c r="BP39" s="38"/>
+      <c r="BQ39" s="38"/>
+      <c r="BR39" s="38"/>
+      <c r="BS39" s="38"/>
+      <c r="BT39" s="38"/>
+      <c r="BU39" s="38"/>
+      <c r="BV39" s="38"/>
+      <c r="BW39" s="38"/>
+      <c r="BX39" s="38"/>
+      <c r="BY39" s="38"/>
+      <c r="BZ39" s="38"/>
+      <c r="CA39" s="38"/>
+      <c r="CB39" s="38"/>
+      <c r="CC39" s="38"/>
     </row>
-    <row r="40" spans="1:81" ht="15" x14ac:dyDescent="0.2">
-      <c r="A40" s="14" t="str" cm="1">
+    <row r="40" spans="1:81" ht="15">
+      <c r="A40" s="32" t="str" cm="1">
         <f t="array" ref="A40">IF($CC40="","",INDEX(Tasks!A$4:A$43,$CC40))</f>
         <v/>
       </c>
-      <c r="B40" s="15" t="str" cm="1">
+      <c r="B40" s="33" t="str" cm="1">
         <f t="array" ref="B40">IF($CC40="","",INDEX(Tasks!B$4:B$43,$CC40))</f>
         <v/>
       </c>
-      <c r="C40" s="16" t="str" cm="1">
+      <c r="C40" s="34" t="str" cm="1">
         <f t="array" ref="C40">IF($CC40="","",INDEX(Tasks!C$4:C$43,$CC40))</f>
         <v/>
       </c>
-      <c r="D40" s="22" t="str" cm="1">
+      <c r="D40" s="35" t="str" cm="1">
         <f t="array" ref="D40">IF($CC40="","",INDEX(Tasks!D$4:D$43,$CC40))</f>
         <v/>
       </c>
-      <c r="E40" s="31" t="str" cm="1">
+      <c r="E40" s="36" t="str" cm="1">
         <f t="array" ref="E40">IF($CC40="","",INDEX(Tasks!E$4:E$43,$CC40))</f>
         <v/>
       </c>
-      <c r="F40" s="22" t="str" cm="1">
+      <c r="F40" s="35" t="str" cm="1">
         <f t="array" ref="F40">IF($CC40="","",INDEX(Tasks!F$4:F$43,$CC40))</f>
         <v/>
       </c>
-      <c r="G40" s="31" t="str" cm="1">
+      <c r="G40" s="36" t="str" cm="1">
         <f t="array" ref="G40">IF($CC40="","",INDEX(Tasks!G$4:G$43,$CC40))</f>
         <v/>
       </c>
-      <c r="H40" s="23" t="str" cm="1">
+      <c r="H40" s="37" t="str" cm="1">
         <f t="array" ref="H40">IF($CC40="","",INDEX(Tasks!H$4:H$43,$CC40))</f>
         <v/>
       </c>
+      <c r="I40" s="38"/>
+      <c r="J40" s="38"/>
+      <c r="K40" s="38"/>
+      <c r="L40" s="38"/>
+      <c r="M40" s="38"/>
+      <c r="N40" s="38"/>
+      <c r="O40" s="38"/>
+      <c r="P40" s="38"/>
+      <c r="Q40" s="38"/>
+      <c r="R40" s="38"/>
+      <c r="S40" s="38"/>
+      <c r="T40" s="38"/>
+      <c r="U40" s="38"/>
+      <c r="V40" s="38"/>
+      <c r="W40" s="38"/>
+      <c r="X40" s="38"/>
+      <c r="Y40" s="38"/>
+      <c r="Z40" s="38"/>
+      <c r="AA40" s="38"/>
+      <c r="AB40" s="38"/>
+      <c r="AC40" s="38"/>
+      <c r="AD40" s="38"/>
+      <c r="AE40" s="38"/>
+      <c r="AF40" s="38"/>
+      <c r="AG40" s="38"/>
+      <c r="AH40" s="38"/>
+      <c r="AI40" s="38"/>
+      <c r="AJ40" s="38"/>
+      <c r="AK40" s="38"/>
+      <c r="AL40" s="38"/>
+      <c r="AM40" s="38"/>
+      <c r="AN40" s="38"/>
+      <c r="AO40" s="38"/>
+      <c r="AP40" s="38"/>
+      <c r="AQ40" s="38"/>
+      <c r="AR40" s="38"/>
+      <c r="AS40" s="38"/>
+      <c r="AT40" s="38"/>
+      <c r="AU40" s="38"/>
+      <c r="AV40" s="38"/>
+      <c r="AW40" s="38"/>
+      <c r="AX40" s="38"/>
+      <c r="AY40" s="38"/>
+      <c r="AZ40" s="38"/>
+      <c r="BA40" s="38"/>
+      <c r="BB40" s="38"/>
+      <c r="BC40" s="38"/>
+      <c r="BD40" s="38"/>
+      <c r="BE40" s="38"/>
+      <c r="BF40" s="38"/>
+      <c r="BG40" s="38"/>
+      <c r="BH40" s="38"/>
+      <c r="BI40" s="38"/>
+      <c r="BJ40" s="38"/>
+      <c r="BK40" s="38"/>
+      <c r="BL40" s="38"/>
+      <c r="BM40" s="38"/>
+      <c r="BN40" s="38"/>
+      <c r="BO40" s="38"/>
+      <c r="BP40" s="38"/>
+      <c r="BQ40" s="38"/>
+      <c r="BR40" s="38"/>
+      <c r="BS40" s="38"/>
+      <c r="BT40" s="38"/>
+      <c r="BU40" s="38"/>
+      <c r="BV40" s="38"/>
+      <c r="BW40" s="38"/>
+      <c r="BX40" s="38"/>
+      <c r="BY40" s="38"/>
+      <c r="BZ40" s="38"/>
+      <c r="CA40" s="38"/>
+      <c r="CB40" s="38"/>
+      <c r="CC40" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -11741,18 +12265,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I43"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" customWidth="1"/>
-    <col min="2" max="2" width="8.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.1640625" customWidth="1"/>
-    <col min="4" max="8" width="8.83203125" customWidth="1"/>
-    <col min="9" max="9" width="37.83203125" customWidth="1"/>
+    <col min="1" max="1" width="2.85546875" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" customWidth="1"/>
+    <col min="4" max="8" width="8.85546875" customWidth="1"/>
+    <col min="9" max="9" width="37.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="25.5" customHeight="1">
       <c r="A1" s="49" t="s">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="B1" s="50"/>
       <c r="C1" s="50"/>
@@ -11763,9 +12287,9 @@
       <c r="H1" s="50"/>
       <c r="I1" s="50"/>
     </row>
-    <row r="2" spans="1:9" ht="10.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="10.35" customHeight="1">
       <c r="A2" s="51" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="B2" s="52"/>
       <c r="C2" s="52"/>
@@ -11776,914 +12300,914 @@
       <c r="H2" s="52"/>
       <c r="I2" s="52"/>
     </row>
-    <row r="3" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" s="29" t="s">
+    <row r="3" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A3" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="25" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A4" s="17">
+        <v>1</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="30" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="20">
-        <v>1</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="25">
+      <c r="E4" s="20">
         <v>45810</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="21">
         <v>4</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="20">
         <f t="shared" ref="G4:G43" si="0">IF(E4="","",E4+F4-1)</f>
         <v>45813</v>
       </c>
-      <c r="H4" s="21">
+      <c r="H4" s="18">
         <v>1</v>
       </c>
-      <c r="I4" s="24"/>
+      <c r="I4" s="19"/>
     </row>
-    <row r="5" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="20">
+    <row r="5" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A5" s="17">
         <v>2</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="20">
+        <v>45811</v>
+      </c>
+      <c r="F5" s="21">
+        <v>3</v>
+      </c>
+      <c r="G5" s="20">
+        <f t="shared" si="0"/>
+        <v>45813</v>
+      </c>
+      <c r="H5" s="18">
+        <v>1</v>
+      </c>
+      <c r="I5" s="19"/>
+    </row>
+    <row r="6" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A6" s="17">
+        <v>3</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="20">
+        <v>45814</v>
+      </c>
+      <c r="F6" s="21">
+        <v>5</v>
+      </c>
+      <c r="G6" s="20">
+        <f t="shared" si="0"/>
+        <v>45818</v>
+      </c>
+      <c r="H6" s="18">
+        <v>1</v>
+      </c>
+      <c r="I6" s="19"/>
+    </row>
+    <row r="7" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A7" s="17">
+        <v>4</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="20">
+        <v>45817</v>
+      </c>
+      <c r="F7" s="21">
+        <v>3</v>
+      </c>
+      <c r="G7" s="20">
+        <f t="shared" si="0"/>
+        <v>45819</v>
+      </c>
+      <c r="H7" s="18">
+        <v>0.8</v>
+      </c>
+      <c r="I7" s="19"/>
+    </row>
+    <row r="8" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A8" s="17">
+        <v>5</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="20">
+        <v>45820</v>
+      </c>
+      <c r="F8" s="21">
+        <v>6</v>
+      </c>
+      <c r="G8" s="20">
+        <f t="shared" si="0"/>
+        <v>45825</v>
+      </c>
+      <c r="H8" s="18">
+        <v>0.6</v>
+      </c>
+      <c r="I8" s="19"/>
+    </row>
+    <row r="9" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A9" s="17">
+        <v>6</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="20">
+        <v>45824</v>
+      </c>
+      <c r="F9" s="21">
+        <v>5</v>
+      </c>
+      <c r="G9" s="20">
+        <f t="shared" si="0"/>
+        <v>45828</v>
+      </c>
+      <c r="H9" s="18">
+        <v>0.2</v>
+      </c>
+      <c r="I9" s="19"/>
+    </row>
+    <row r="10" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A10" s="17">
+        <v>7</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="20">
+        <v>45826</v>
+      </c>
+      <c r="F10" s="21">
+        <v>3</v>
+      </c>
+      <c r="G10" s="20">
+        <f t="shared" si="0"/>
+        <v>45828</v>
+      </c>
+      <c r="H10" s="18">
+        <v>0</v>
+      </c>
+      <c r="I10" s="19"/>
+    </row>
+    <row r="11" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A11" s="17">
+        <v>8</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="20">
+        <v>45829</v>
+      </c>
+      <c r="F11" s="21">
+        <v>14</v>
+      </c>
+      <c r="G11" s="20">
+        <f t="shared" si="0"/>
+        <v>45842</v>
+      </c>
+      <c r="H11" s="18">
+        <v>0</v>
+      </c>
+      <c r="I11" s="19"/>
+    </row>
+    <row r="12" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A12" s="17">
+        <v>9</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="20">
+        <v>45832</v>
+      </c>
+      <c r="F12" s="21">
+        <v>10</v>
+      </c>
+      <c r="G12" s="20">
+        <f t="shared" si="0"/>
+        <v>45841</v>
+      </c>
+      <c r="H12" s="18">
+        <v>0</v>
+      </c>
+      <c r="I12" s="19"/>
+    </row>
+    <row r="13" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A13" s="17">
+        <v>10</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="20">
+        <v>45829</v>
+      </c>
+      <c r="F13" s="21">
+        <v>12</v>
+      </c>
+      <c r="G13" s="20">
+        <f t="shared" si="0"/>
+        <v>45840</v>
+      </c>
+      <c r="H13" s="18">
+        <v>0</v>
+      </c>
+      <c r="I13" s="19"/>
+    </row>
+    <row r="14" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A14" s="17">
+        <v>11</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="20">
+        <v>45840</v>
+      </c>
+      <c r="F14" s="21">
+        <v>8</v>
+      </c>
+      <c r="G14" s="20">
+        <f t="shared" si="0"/>
+        <v>45847</v>
+      </c>
+      <c r="H14" s="18">
+        <v>0</v>
+      </c>
+      <c r="I14" s="19"/>
+    </row>
+    <row r="15" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A15" s="17">
+        <v>12</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="20">
+        <v>45841</v>
+      </c>
+      <c r="F15" s="21">
+        <v>10</v>
+      </c>
+      <c r="G15" s="20">
+        <f t="shared" si="0"/>
+        <v>45850</v>
+      </c>
+      <c r="H15" s="18">
+        <v>0</v>
+      </c>
+      <c r="I15" s="19"/>
+    </row>
+    <row r="16" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A16" s="17">
         <v>13</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="B16" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5" s="25">
-        <v>45811</v>
-      </c>
-      <c r="F5" s="26">
+      <c r="C16" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="20">
+        <v>45850</v>
+      </c>
+      <c r="F16" s="21">
+        <v>6</v>
+      </c>
+      <c r="G16" s="20">
+        <f t="shared" si="0"/>
+        <v>45855</v>
+      </c>
+      <c r="H16" s="18">
+        <v>0</v>
+      </c>
+      <c r="I16" s="19"/>
+    </row>
+    <row r="17" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A17" s="17">
+        <v>14</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="20">
+        <v>45854</v>
+      </c>
+      <c r="F17" s="21">
+        <v>5</v>
+      </c>
+      <c r="G17" s="20">
+        <f t="shared" si="0"/>
+        <v>45858</v>
+      </c>
+      <c r="H17" s="18">
+        <v>0</v>
+      </c>
+      <c r="I17" s="19"/>
+    </row>
+    <row r="18" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A18" s="17">
+        <v>15</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="20">
+        <v>45856</v>
+      </c>
+      <c r="F18" s="21">
+        <v>5</v>
+      </c>
+      <c r="G18" s="20">
+        <f t="shared" si="0"/>
+        <v>45860</v>
+      </c>
+      <c r="H18" s="18">
+        <v>0</v>
+      </c>
+      <c r="I18" s="19"/>
+    </row>
+    <row r="19" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A19" s="17">
+        <v>16</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="20">
+        <v>45858</v>
+      </c>
+      <c r="F19" s="21">
+        <v>5</v>
+      </c>
+      <c r="G19" s="20">
+        <f t="shared" si="0"/>
+        <v>45862</v>
+      </c>
+      <c r="H19" s="18">
+        <v>0</v>
+      </c>
+      <c r="I19" s="19"/>
+    </row>
+    <row r="20" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A20" s="17">
+        <v>17</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="20">
+        <v>45864</v>
+      </c>
+      <c r="F20" s="21">
+        <v>4</v>
+      </c>
+      <c r="G20" s="20">
+        <f t="shared" si="0"/>
+        <v>45867</v>
+      </c>
+      <c r="H20" s="18">
+        <v>0</v>
+      </c>
+      <c r="I20" s="19"/>
+    </row>
+    <row r="21" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A21" s="17">
+        <v>18</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="20">
+        <v>45867</v>
+      </c>
+      <c r="F21" s="21">
         <v>3</v>
       </c>
-      <c r="G5" s="25">
-        <f t="shared" si="0"/>
-        <v>45813</v>
-      </c>
-      <c r="H5" s="21">
-        <v>1</v>
-      </c>
-      <c r="I5" s="24"/>
+      <c r="G21" s="20">
+        <f t="shared" si="0"/>
+        <v>45869</v>
+      </c>
+      <c r="H21" s="18">
+        <v>0</v>
+      </c>
+      <c r="I21" s="19"/>
     </row>
-    <row r="6" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="20">
-        <v>3</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="24" t="s">
+    <row r="22" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A22" s="17">
+        <v>19</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="20">
+        <v>45868</v>
+      </c>
+      <c r="F22" s="21">
+        <v>5</v>
+      </c>
+      <c r="G22" s="20">
+        <f t="shared" si="0"/>
+        <v>45872</v>
+      </c>
+      <c r="H22" s="18">
+        <v>0</v>
+      </c>
+      <c r="I22" s="19"/>
+    </row>
+    <row r="23" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A23" s="17">
+        <v>20</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="20">
+        <v>45873</v>
+      </c>
+      <c r="F23" s="21">
+        <v>2</v>
+      </c>
+      <c r="G23" s="20">
+        <f t="shared" si="0"/>
+        <v>45874</v>
+      </c>
+      <c r="H23" s="18">
+        <v>0</v>
+      </c>
+      <c r="I23" s="19"/>
+    </row>
+    <row r="24" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A24" s="17">
+        <v>21</v>
+      </c>
+      <c r="B24" s="17"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H24" s="17"/>
+      <c r="I24" s="19"/>
+    </row>
+    <row r="25" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A25" s="17">
+        <v>22</v>
+      </c>
+      <c r="B25" s="17"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H25" s="17"/>
+      <c r="I25" s="19"/>
+    </row>
+    <row r="26" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A26" s="17">
+        <v>23</v>
+      </c>
+      <c r="B26" s="17"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H26" s="17"/>
+      <c r="I26" s="19"/>
+    </row>
+    <row r="27" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A27" s="17">
+        <v>24</v>
+      </c>
+      <c r="B27" s="17"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H27" s="17"/>
+      <c r="I27" s="19"/>
+    </row>
+    <row r="28" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A28" s="17">
+        <v>25</v>
+      </c>
+      <c r="B28" s="17"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H28" s="17"/>
+      <c r="I28" s="19"/>
+    </row>
+    <row r="29" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A29" s="17">
+        <v>26</v>
+      </c>
+      <c r="B29" s="17"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H29" s="17"/>
+      <c r="I29" s="19"/>
+    </row>
+    <row r="30" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A30" s="17">
+        <v>27</v>
+      </c>
+      <c r="B30" s="17"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H30" s="17"/>
+      <c r="I30" s="19"/>
+    </row>
+    <row r="31" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A31" s="17">
+        <v>28</v>
+      </c>
+      <c r="B31" s="17"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H31" s="17"/>
+      <c r="I31" s="19"/>
+    </row>
+    <row r="32" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A32" s="17">
+        <v>29</v>
+      </c>
+      <c r="B32" s="17"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H32" s="17"/>
+      <c r="I32" s="19"/>
+    </row>
+    <row r="33" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A33" s="17">
+        <v>30</v>
+      </c>
+      <c r="B33" s="17"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H33" s="17"/>
+      <c r="I33" s="19"/>
+    </row>
+    <row r="34" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A34" s="17">
+        <v>31</v>
+      </c>
+      <c r="B34" s="17"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H34" s="17"/>
+      <c r="I34" s="19"/>
+    </row>
+    <row r="35" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A35" s="17">
+        <v>32</v>
+      </c>
+      <c r="B35" s="17"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H35" s="17"/>
+      <c r="I35" s="19"/>
+    </row>
+    <row r="36" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A36" s="17">
+        <v>33</v>
+      </c>
+      <c r="B36" s="17"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H36" s="17"/>
+      <c r="I36" s="19"/>
+    </row>
+    <row r="37" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A37" s="17">
+        <v>34</v>
+      </c>
+      <c r="B37" s="17"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H37" s="17"/>
+      <c r="I37" s="19"/>
+    </row>
+    <row r="38" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A38" s="17">
         <v>35</v>
       </c>
-      <c r="D6" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" s="25">
-        <v>45814</v>
-      </c>
-      <c r="F6" s="26">
-        <v>5</v>
-      </c>
-      <c r="G6" s="25">
-        <f t="shared" si="0"/>
-        <v>45818</v>
-      </c>
-      <c r="H6" s="21">
-        <v>1</v>
-      </c>
-      <c r="I6" s="24"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H38" s="17"/>
+      <c r="I38" s="19"/>
     </row>
-    <row r="7" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="20">
-        <v>4</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="24" t="s">
+    <row r="39" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A39" s="17">
         <v>36</v>
       </c>
-      <c r="D7" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="25">
-        <v>45817</v>
-      </c>
-      <c r="F7" s="26">
-        <v>3</v>
-      </c>
-      <c r="G7" s="25">
-        <f t="shared" si="0"/>
-        <v>45819</v>
-      </c>
-      <c r="H7" s="21">
-        <v>0.8</v>
-      </c>
-      <c r="I7" s="24"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H39" s="17"/>
+      <c r="I39" s="19"/>
     </row>
-    <row r="8" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="20">
-        <v>5</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="24" t="s">
+    <row r="40" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A40" s="17">
         <v>37</v>
       </c>
-      <c r="D8" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" s="25">
-        <v>45820</v>
-      </c>
-      <c r="F8" s="26">
-        <v>6</v>
-      </c>
-      <c r="G8" s="25">
-        <f t="shared" si="0"/>
-        <v>45825</v>
-      </c>
-      <c r="H8" s="21">
-        <v>0.6</v>
-      </c>
-      <c r="I8" s="24"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H40" s="17"/>
+      <c r="I40" s="19"/>
     </row>
-    <row r="9" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20">
-        <v>6</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="24" t="s">
+    <row r="41" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A41" s="17">
         <v>38</v>
       </c>
-      <c r="D9" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E9" s="25">
-        <v>45824</v>
-      </c>
-      <c r="F9" s="26">
-        <v>5</v>
-      </c>
-      <c r="G9" s="25">
-        <f t="shared" si="0"/>
-        <v>45828</v>
-      </c>
-      <c r="H9" s="21">
-        <v>0.2</v>
-      </c>
-      <c r="I9" s="24"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H41" s="17"/>
+      <c r="I41" s="19"/>
     </row>
-    <row r="10" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20">
-        <v>7</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="24" t="s">
+    <row r="42" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A42" s="17">
         <v>39</v>
       </c>
-      <c r="D10" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="E10" s="25">
-        <v>45826</v>
-      </c>
-      <c r="F10" s="26">
-        <v>3</v>
-      </c>
-      <c r="G10" s="25">
-        <f t="shared" si="0"/>
-        <v>45828</v>
-      </c>
-      <c r="H10" s="21">
-        <v>0</v>
-      </c>
-      <c r="I10" s="24"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H42" s="17"/>
+      <c r="I42" s="19"/>
     </row>
-    <row r="11" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20">
-        <v>8</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="24" t="s">
+    <row r="43" spans="1:9" ht="15.95" customHeight="1">
+      <c r="A43" s="17">
         <v>40</v>
       </c>
-      <c r="D11" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" s="25">
-        <v>45829</v>
-      </c>
-      <c r="F11" s="26">
-        <v>14</v>
-      </c>
-      <c r="G11" s="25">
-        <f t="shared" si="0"/>
-        <v>45842</v>
-      </c>
-      <c r="H11" s="21">
-        <v>0</v>
-      </c>
-      <c r="I11" s="24"/>
-    </row>
-    <row r="12" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20">
-        <v>9</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" s="25">
-        <v>45832</v>
-      </c>
-      <c r="F12" s="26">
-        <v>10</v>
-      </c>
-      <c r="G12" s="25">
-        <f t="shared" si="0"/>
-        <v>45841</v>
-      </c>
-      <c r="H12" s="21">
-        <v>0</v>
-      </c>
-      <c r="I12" s="24"/>
-    </row>
-    <row r="13" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20">
-        <v>10</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" s="25">
-        <v>45829</v>
-      </c>
-      <c r="F13" s="26">
-        <v>12</v>
-      </c>
-      <c r="G13" s="25">
-        <f t="shared" si="0"/>
-        <v>45840</v>
-      </c>
-      <c r="H13" s="21">
-        <v>0</v>
-      </c>
-      <c r="I13" s="24"/>
-    </row>
-    <row r="14" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20">
-        <v>11</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="E14" s="25">
-        <v>45840</v>
-      </c>
-      <c r="F14" s="26">
-        <v>8</v>
-      </c>
-      <c r="G14" s="25">
-        <f t="shared" si="0"/>
-        <v>45847</v>
-      </c>
-      <c r="H14" s="21">
-        <v>0</v>
-      </c>
-      <c r="I14" s="24"/>
-    </row>
-    <row r="15" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20">
-        <v>12</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" s="25">
-        <v>45841</v>
-      </c>
-      <c r="F15" s="26">
-        <v>10</v>
-      </c>
-      <c r="G15" s="25">
-        <f t="shared" si="0"/>
-        <v>45850</v>
-      </c>
-      <c r="H15" s="21">
-        <v>0</v>
-      </c>
-      <c r="I15" s="24"/>
-    </row>
-    <row r="16" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20">
-        <v>13</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="25">
-        <v>45850</v>
-      </c>
-      <c r="F16" s="26">
-        <v>6</v>
-      </c>
-      <c r="G16" s="25">
-        <f t="shared" si="0"/>
-        <v>45855</v>
-      </c>
-      <c r="H16" s="21">
-        <v>0</v>
-      </c>
-      <c r="I16" s="24"/>
-    </row>
-    <row r="17" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20">
-        <v>14</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E17" s="25">
-        <v>45854</v>
-      </c>
-      <c r="F17" s="26">
-        <v>5</v>
-      </c>
-      <c r="G17" s="25">
-        <f t="shared" si="0"/>
-        <v>45858</v>
-      </c>
-      <c r="H17" s="21">
-        <v>0</v>
-      </c>
-      <c r="I17" s="24"/>
-    </row>
-    <row r="18" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20">
-        <v>15</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E18" s="25">
-        <v>45856</v>
-      </c>
-      <c r="F18" s="26">
-        <v>5</v>
-      </c>
-      <c r="G18" s="25">
-        <f t="shared" si="0"/>
-        <v>45860</v>
-      </c>
-      <c r="H18" s="21">
-        <v>0</v>
-      </c>
-      <c r="I18" s="24"/>
-    </row>
-    <row r="19" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="20">
-        <v>16</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="E19" s="25">
-        <v>45858</v>
-      </c>
-      <c r="F19" s="26">
-        <v>5</v>
-      </c>
-      <c r="G19" s="25">
-        <f t="shared" si="0"/>
-        <v>45862</v>
-      </c>
-      <c r="H19" s="21">
-        <v>0</v>
-      </c>
-      <c r="I19" s="24"/>
-    </row>
-    <row r="20" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="20">
-        <v>17</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="E20" s="25">
-        <v>45864</v>
-      </c>
-      <c r="F20" s="26">
-        <v>4</v>
-      </c>
-      <c r="G20" s="25">
-        <f t="shared" si="0"/>
-        <v>45867</v>
-      </c>
-      <c r="H20" s="21">
-        <v>0</v>
-      </c>
-      <c r="I20" s="24"/>
-    </row>
-    <row r="21" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="20">
-        <v>18</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E21" s="25">
-        <v>45867</v>
-      </c>
-      <c r="F21" s="26">
-        <v>3</v>
-      </c>
-      <c r="G21" s="25">
-        <f t="shared" si="0"/>
-        <v>45869</v>
-      </c>
-      <c r="H21" s="21">
-        <v>0</v>
-      </c>
-      <c r="I21" s="24"/>
-    </row>
-    <row r="22" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="20">
-        <v>19</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E22" s="25">
-        <v>45868</v>
-      </c>
-      <c r="F22" s="26">
-        <v>5</v>
-      </c>
-      <c r="G22" s="25">
-        <f t="shared" si="0"/>
-        <v>45872</v>
-      </c>
-      <c r="H22" s="21">
-        <v>0</v>
-      </c>
-      <c r="I22" s="24"/>
-    </row>
-    <row r="23" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="20">
-        <v>20</v>
-      </c>
-      <c r="B23" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="E23" s="25">
-        <v>45873</v>
-      </c>
-      <c r="F23" s="26">
-        <v>2</v>
-      </c>
-      <c r="G23" s="25">
-        <f t="shared" si="0"/>
-        <v>45874</v>
-      </c>
-      <c r="H23" s="21">
-        <v>0</v>
-      </c>
-      <c r="I23" s="24"/>
-    </row>
-    <row r="24" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="20">
-        <v>21</v>
-      </c>
-      <c r="B24" s="20"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H24" s="20"/>
-      <c r="I24" s="24"/>
-    </row>
-    <row r="25" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="20">
-        <v>22</v>
-      </c>
-      <c r="B25" s="20"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H25" s="20"/>
-      <c r="I25" s="24"/>
-    </row>
-    <row r="26" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="20">
-        <v>23</v>
-      </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H26" s="20"/>
-      <c r="I26" s="24"/>
-    </row>
-    <row r="27" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="20">
-        <v>24</v>
-      </c>
-      <c r="B27" s="20"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H27" s="20"/>
-      <c r="I27" s="24"/>
-    </row>
-    <row r="28" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="20">
-        <v>25</v>
-      </c>
-      <c r="B28" s="20"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H28" s="20"/>
-      <c r="I28" s="24"/>
-    </row>
-    <row r="29" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="20">
-        <v>26</v>
-      </c>
-      <c r="B29" s="20"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H29" s="20"/>
-      <c r="I29" s="24"/>
-    </row>
-    <row r="30" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="20">
-        <v>27</v>
-      </c>
-      <c r="B30" s="20"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H30" s="20"/>
-      <c r="I30" s="24"/>
-    </row>
-    <row r="31" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="20">
-        <v>28</v>
-      </c>
-      <c r="B31" s="20"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H31" s="20"/>
-      <c r="I31" s="24"/>
-    </row>
-    <row r="32" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="20">
-        <v>29</v>
-      </c>
-      <c r="B32" s="20"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H32" s="20"/>
-      <c r="I32" s="24"/>
-    </row>
-    <row r="33" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="20">
-        <v>30</v>
-      </c>
-      <c r="B33" s="20"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H33" s="20"/>
-      <c r="I33" s="24"/>
-    </row>
-    <row r="34" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="20">
-        <v>31</v>
-      </c>
-      <c r="B34" s="20"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H34" s="20"/>
-      <c r="I34" s="24"/>
-    </row>
-    <row r="35" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="20">
-        <v>32</v>
-      </c>
-      <c r="B35" s="20"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H35" s="20"/>
-      <c r="I35" s="24"/>
-    </row>
-    <row r="36" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="20">
-        <v>33</v>
-      </c>
-      <c r="B36" s="20"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H36" s="20"/>
-      <c r="I36" s="24"/>
-    </row>
-    <row r="37" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="20">
-        <v>34</v>
-      </c>
-      <c r="B37" s="20"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="25"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H37" s="20"/>
-      <c r="I37" s="24"/>
-    </row>
-    <row r="38" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="20">
-        <v>35</v>
-      </c>
-      <c r="B38" s="20"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="25"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H38" s="20"/>
-      <c r="I38" s="24"/>
-    </row>
-    <row r="39" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="20">
-        <v>36</v>
-      </c>
-      <c r="B39" s="20"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H39" s="20"/>
-      <c r="I39" s="24"/>
-    </row>
-    <row r="40" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="20">
-        <v>37</v>
-      </c>
-      <c r="B40" s="20"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H40" s="20"/>
-      <c r="I40" s="24"/>
-    </row>
-    <row r="41" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="20">
-        <v>38</v>
-      </c>
-      <c r="B41" s="20"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="25"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H41" s="20"/>
-      <c r="I41" s="24"/>
-    </row>
-    <row r="42" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="20">
-        <v>39</v>
-      </c>
-      <c r="B42" s="20"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="25"/>
-      <c r="F42" s="20"/>
-      <c r="G42" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H42" s="20"/>
-      <c r="I42" s="24"/>
-    </row>
-    <row r="43" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="20">
-        <v>40</v>
-      </c>
-      <c r="B43" s="20"/>
-      <c r="C43" s="24"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="25"/>
-      <c r="F43" s="20"/>
-      <c r="G43" s="25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H43" s="20"/>
-      <c r="I43" s="24"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H43" s="17"/>
+      <c r="I43" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -12753,150 +13277,163 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="3" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" customWidth="1"/>
-    <col min="3" max="3" width="33.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" customWidth="1"/>
+    <col min="3" max="3" width="33.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="25.5" customHeight="1">
       <c r="A1" s="53" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B1" s="54"/>
       <c r="C1" s="54"/>
-      <c r="D1" s="48"/>
+      <c r="D1" s="55"/>
     </row>
-    <row r="2" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="15.95" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>2</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="D2" s="38"/>
     </row>
-    <row r="3" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="15.95" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="B3" s="7">
         <f ca="1">B5</f>
-        <v>46198</v>
+        <v>46206</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>4</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D3" s="38"/>
     </row>
-    <row r="4" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="15.95" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="B4" s="8">
         <v>70</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>6</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="D4" s="38"/>
     </row>
-    <row r="5" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="15.95" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="B5" s="10">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46206</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>59</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="D5" s="38"/>
     </row>
-    <row r="6" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="15.95" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="C6" s="9"/>
+      <c r="D6" s="38"/>
     </row>
-    <row r="7" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="15.95" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="C7" s="9"/>
+      <c r="D7" s="38"/>
     </row>
-    <row r="8" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="15.95" customHeight="1">
       <c r="A8" s="5" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="9"/>
+      <c r="D8" s="38"/>
     </row>
-    <row r="9" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="15.95" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="9"/>
+      <c r="D9" s="38"/>
     </row>
-    <row r="10" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="15.95" customHeight="1">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
+      <c r="D10" s="38"/>
     </row>
-    <row r="11" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="55"/>
-      <c r="C11" s="55"/>
-      <c r="D11" s="48"/>
+    <row r="11" spans="1:4" ht="15.95" customHeight="1">
+      <c r="A11" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="55"/>
     </row>
-    <row r="13" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="32" t="s">
-        <v>13</v>
+    <row r="13" spans="1:4" ht="15.95" customHeight="1">
+      <c r="A13" s="26" t="s">
+        <v>17</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
+      <c r="D13" s="38"/>
     </row>
-    <row r="14" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="33" t="s">
-        <v>14</v>
+    <row r="14" spans="1:4" ht="15.95" customHeight="1">
+      <c r="A14" s="27" t="s">
+        <v>24</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
+      <c r="D14" s="38"/>
     </row>
-    <row r="15" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="34" t="s">
-        <v>53</v>
+    <row r="15" spans="1:4" ht="15.95" customHeight="1">
+      <c r="A15" s="28" t="s">
+        <v>28</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
+      <c r="D15" s="38"/>
     </row>
-    <row r="16" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="36" t="s">
-        <v>15</v>
+    <row r="16" spans="1:4" ht="15.95" customHeight="1">
+      <c r="A16" s="30" t="s">
+        <v>34</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
+      <c r="D16" s="38"/>
     </row>
-    <row r="17" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="35" t="s">
-        <v>16</v>
+    <row r="17" spans="1:3" ht="15.95" customHeight="1">
+      <c r="A17" s="29" t="s">
+        <v>39</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
     </row>
-    <row r="18" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="37" t="s">
-        <v>17</v>
+    <row r="18" spans="1:3" ht="15.95" customHeight="1">
+      <c r="A18" s="31" t="s">
+        <v>59</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -12908,4 +13445,26 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2377950-0DE1-460F-9A9C-2BF76E7C44F4}">
+  <dimension ref="A2:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="16.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2">
+      <c r="A2" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="38">
+        <f ca="1">NOW()</f>
+        <v>46206.496841550928</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>